--- a/research/traditional_assets/database/data/cayman_islands/cayman_islands_retail_automotive.xlsx
+++ b/research/traditional_assets/database/data/cayman_islands/cayman_islands_retail_automotive.xlsx
@@ -1127,43 +1127,43 @@
         <v>0.448979591836735</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>126.86069697032</v>
       </c>
       <c r="G2">
         <v>10.1733333333333</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.225666666666667</v>
       </c>
       <c r="I2">
         <v>0.450812407680945</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>185.9</v>
       </c>
       <c r="L2">
-        <v>401.223325225222</v>
+        <v>397.355918395619</v>
       </c>
       <c r="M2">
         <v>328.66</v>
       </c>
       <c r="N2">
-        <v>391.383325225222</v>
+        <v>390.900918395619</v>
       </c>
       <c r="O2">
         <v>152.6</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>3.385</v>
       </c>
       <c r="Q2">
         <v>0.089223139991442</v>
       </c>
       <c r="R2">
-        <v>0.08226412166735721</v>
+        <v>0.0823091216673572</v>
       </c>
       <c r="S2">
         <v>0.0612366166625341</v>
@@ -1185,13 +1185,13 @@
         <v>0.112196477592256</v>
       </c>
       <c r="X2">
-        <v>0.08226412166735721</v>
+        <v>0.08263244612864371</v>
       </c>
       <c r="Y2">
         <v>1.29419093197183</v>
       </c>
       <c r="Z2">
-        <v>0.710753601930761</v>
+        <v>0.717932931243193</v>
       </c>
       <c r="AA2">
         <v>152.6</v>
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08226412166735722</v>
+        <v>0.08230912166735722</v>
       </c>
       <c r="C2">
-        <v>401.2233252252221</v>
+        <v>397.3559183956193</v>
       </c>
       <c r="D2">
-        <v>391.3833252252221</v>
+        <v>390.9009183956193</v>
       </c>
       <c r="E2">
-        <v>-152.6</v>
+        <v>-149.215</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.385</v>
       </c>
       <c r="G2">
         <v>9.84</v>
@@ -1445,28 +1445,28 @@
         <v>21.6</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1702655</v>
       </c>
       <c r="N2">
-        <v>21.6</v>
+        <v>21.4297345</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>21.6</v>
+        <v>21.4297345</v>
       </c>
       <c r="Q2">
-        <v>30</v>
+        <v>29.8297345</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08226412166735722</v>
+        <v>0.08263244612864366</v>
       </c>
       <c r="T2">
-        <v>0.7107536019307608</v>
+        <v>0.7179329312431927</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>126.8606969703199</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08230912166735722</v>
+        <v>0.08235412166735723</v>
       </c>
       <c r="C3">
-        <v>397.3559183956193</v>
+        <v>393.4896993011521</v>
       </c>
       <c r="D3">
-        <v>390.9009183956193</v>
+        <v>390.4196993011521</v>
       </c>
       <c r="E3">
-        <v>-149.215</v>
+        <v>-145.83</v>
       </c>
       <c r="F3">
-        <v>3.385</v>
+        <v>6.77</v>
       </c>
       <c r="G3">
         <v>9.84</v>
@@ -1527,28 +1527,28 @@
         <v>21.6</v>
       </c>
       <c r="M3">
-        <v>0.1702655</v>
+        <v>0.340531</v>
       </c>
       <c r="N3">
-        <v>21.4297345</v>
+        <v>21.259469</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>21.4297345</v>
+        <v>21.259469</v>
       </c>
       <c r="Q3">
-        <v>29.8297345</v>
+        <v>29.659469</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08263244612864366</v>
+        <v>0.08300828741567065</v>
       </c>
       <c r="T3">
-        <v>0.7179329312431927</v>
+        <v>0.7252587774803682</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>126.8606969703199</v>
+        <v>63.43034848515995</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08235412166735723</v>
+        <v>0.08239912166735722</v>
       </c>
       <c r="C4">
-        <v>393.4896993011521</v>
+        <v>389.6246635607258</v>
       </c>
       <c r="D4">
-        <v>390.4196993011521</v>
+        <v>389.9396635607258</v>
       </c>
       <c r="E4">
-        <v>-145.83</v>
+        <v>-142.445</v>
       </c>
       <c r="F4">
-        <v>6.77</v>
+        <v>10.155</v>
       </c>
       <c r="G4">
         <v>9.84</v>
@@ -1609,28 +1609,28 @@
         <v>21.6</v>
       </c>
       <c r="M4">
-        <v>0.340531</v>
+        <v>0.5107965</v>
       </c>
       <c r="N4">
-        <v>21.259469</v>
+        <v>21.0892035</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>21.259469</v>
+        <v>21.0892035</v>
       </c>
       <c r="Q4">
-        <v>29.659469</v>
+        <v>29.4892035</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08300828741567065</v>
+        <v>0.08339187800758477</v>
       </c>
       <c r="T4">
-        <v>0.7252587774803682</v>
+        <v>0.7327356720935677</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>63.43034848515995</v>
+        <v>42.28689899010663</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08239912166735722</v>
+        <v>0.08244412166735723</v>
       </c>
       <c r="C5">
-        <v>389.6246635607258</v>
+        <v>385.7608068147644</v>
       </c>
       <c r="D5">
-        <v>389.9396635607258</v>
+        <v>389.4608068147645</v>
       </c>
       <c r="E5">
-        <v>-142.445</v>
+        <v>-139.06</v>
       </c>
       <c r="F5">
-        <v>10.155</v>
+        <v>13.54</v>
       </c>
       <c r="G5">
         <v>9.84</v>
@@ -1691,28 +1691,28 @@
         <v>21.6</v>
       </c>
       <c r="M5">
-        <v>0.5107965</v>
+        <v>0.6810620000000001</v>
       </c>
       <c r="N5">
-        <v>21.0892035</v>
+        <v>20.918938</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>21.0892035</v>
+        <v>20.918938</v>
       </c>
       <c r="Q5">
-        <v>29.4892035</v>
+        <v>29.318938</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08339187800758477</v>
+        <v>0.08378346007016378</v>
       </c>
       <c r="T5">
-        <v>0.7327356720935677</v>
+        <v>0.7403683353445425</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>42.28689899010663</v>
+        <v>31.71517424257997</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08244412166735723</v>
+        <v>0.08248912166735722</v>
       </c>
       <c r="C6">
-        <v>385.7608068147644</v>
+        <v>381.8981247250824</v>
       </c>
       <c r="D6">
-        <v>389.4608068147645</v>
+        <v>388.9831247250825</v>
       </c>
       <c r="E6">
-        <v>-139.06</v>
+        <v>-135.675</v>
       </c>
       <c r="F6">
-        <v>13.54</v>
+        <v>16.925</v>
       </c>
       <c r="G6">
         <v>9.84</v>
@@ -1773,28 +1773,28 @@
         <v>21.6</v>
       </c>
       <c r="M6">
-        <v>0.6810620000000001</v>
+        <v>0.8513275</v>
       </c>
       <c r="N6">
-        <v>20.918938</v>
+        <v>20.7486725</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>20.918938</v>
+        <v>20.7486725</v>
       </c>
       <c r="Q6">
-        <v>29.318938</v>
+        <v>29.1486725</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08378346007016378</v>
+        <v>0.08418328596563918</v>
       </c>
       <c r="T6">
-        <v>0.7403683353445425</v>
+        <v>0.748161686242906</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>31.71517424257997</v>
+        <v>25.37213939406398</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08248912166735722</v>
+        <v>0.08253412166735724</v>
       </c>
       <c r="C7">
-        <v>381.8981247250824</v>
+        <v>378.0366129747501</v>
       </c>
       <c r="D7">
-        <v>388.9831247250825</v>
+        <v>388.5066129747501</v>
       </c>
       <c r="E7">
-        <v>-135.675</v>
+        <v>-132.29</v>
       </c>
       <c r="F7">
-        <v>16.925</v>
+        <v>20.31</v>
       </c>
       <c r="G7">
         <v>9.84</v>
@@ -1855,28 +1855,28 @@
         <v>21.6</v>
       </c>
       <c r="M7">
-        <v>0.8513275</v>
+        <v>1.021593</v>
       </c>
       <c r="N7">
-        <v>20.7486725</v>
+        <v>20.578407</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>20.7486725</v>
+        <v>20.578407</v>
       </c>
       <c r="Q7">
-        <v>29.1486725</v>
+        <v>28.978407</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08418328596563918</v>
+        <v>0.08459161879506089</v>
       </c>
       <c r="T7">
-        <v>0.748161686242906</v>
+        <v>0.7561208531178306</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>25.37213939406398</v>
+        <v>21.14344949505332</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08253412166735724</v>
+        <v>0.08257912166735722</v>
       </c>
       <c r="C8">
-        <v>378.0366129747501</v>
+        <v>374.1762672679663</v>
       </c>
       <c r="D8">
-        <v>388.5066129747501</v>
+        <v>388.0312672679663</v>
       </c>
       <c r="E8">
-        <v>-132.29</v>
+        <v>-128.905</v>
       </c>
       <c r="F8">
-        <v>20.31</v>
+        <v>23.695</v>
       </c>
       <c r="G8">
         <v>9.84</v>
@@ -1937,28 +1937,28 @@
         <v>21.6</v>
       </c>
       <c r="M8">
-        <v>1.021593</v>
+        <v>1.1918585</v>
       </c>
       <c r="N8">
-        <v>20.578407</v>
+        <v>20.4081415</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>20.578407</v>
+        <v>20.4081415</v>
       </c>
       <c r="Q8">
-        <v>28.978407</v>
+        <v>28.8081415</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08459161879506089</v>
+        <v>0.08500873297565292</v>
       </c>
       <c r="T8">
-        <v>0.7561208531178306</v>
+        <v>0.7642511848717857</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>21.14344949505332</v>
+        <v>18.1229567100457</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0825791216673572</v>
+        <v>0.08262412166735723</v>
       </c>
       <c r="C9">
-        <v>374.1762672679665</v>
+        <v>370.3170833299271</v>
       </c>
       <c r="D9">
-        <v>388.0312672679665</v>
+        <v>387.5570833299271</v>
       </c>
       <c r="E9">
-        <v>-128.905</v>
+        <v>-125.52</v>
       </c>
       <c r="F9">
-        <v>23.695</v>
+        <v>27.08</v>
       </c>
       <c r="G9">
         <v>9.84</v>
@@ -2019,28 +2019,28 @@
         <v>21.6</v>
       </c>
       <c r="M9">
-        <v>1.1918585</v>
+        <v>1.362124</v>
       </c>
       <c r="N9">
-        <v>20.4081415</v>
+        <v>20.237876</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>20.4081415</v>
+        <v>20.237876</v>
       </c>
       <c r="Q9">
-        <v>28.8081415</v>
+        <v>28.637876</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08500873297565292</v>
+        <v>0.08543491485582308</v>
       </c>
       <c r="T9">
-        <v>0.7642511848717857</v>
+        <v>0.7725582629682182</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>18.1229567100457</v>
+        <v>15.85758712128998</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08262412166735723</v>
+        <v>0.08266912166735724</v>
       </c>
       <c r="C10">
-        <v>370.3170833299271</v>
+        <v>366.4590569066996</v>
       </c>
       <c r="D10">
-        <v>387.5570833299271</v>
+        <v>387.0840569066996</v>
       </c>
       <c r="E10">
-        <v>-125.52</v>
+        <v>-122.135</v>
       </c>
       <c r="F10">
-        <v>27.08</v>
+        <v>30.465</v>
       </c>
       <c r="G10">
         <v>9.84</v>
@@ -2101,28 +2101,28 @@
         <v>21.6</v>
       </c>
       <c r="M10">
-        <v>1.362124</v>
+        <v>1.5323895</v>
       </c>
       <c r="N10">
-        <v>20.237876</v>
+        <v>20.0676105</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>20.237876</v>
+        <v>20.0676105</v>
       </c>
       <c r="Q10">
-        <v>28.637876</v>
+        <v>28.4676105</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08543491485582308</v>
+        <v>0.08587046337072224</v>
       </c>
       <c r="T10">
-        <v>0.7725582629682182</v>
+        <v>0.7810479142096273</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>15.85758712128998</v>
+        <v>14.09563299670221</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08266912166735724</v>
+        <v>0.08286412166735722</v>
       </c>
       <c r="C11">
-        <v>366.4590569066996</v>
+        <v>361.0375486150899</v>
       </c>
       <c r="D11">
-        <v>387.0840569066996</v>
+        <v>385.04754861509</v>
       </c>
       <c r="E11">
-        <v>-122.135</v>
+        <v>-118.75</v>
       </c>
       <c r="F11">
-        <v>30.465</v>
+        <v>33.84999999999999</v>
       </c>
       <c r="G11">
         <v>9.84</v>
@@ -2183,45 +2183,45 @@
         <v>21.6</v>
       </c>
       <c r="M11">
-        <v>1.5323895</v>
+        <v>1.75343</v>
       </c>
       <c r="N11">
-        <v>20.0676105</v>
+        <v>19.84657</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>20.0676105</v>
+        <v>19.84657</v>
       </c>
       <c r="Q11">
-        <v>28.4676105</v>
+        <v>28.24657000000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08587046337072224</v>
+        <v>0.08631569074150802</v>
       </c>
       <c r="T11">
-        <v>0.7810479142096273</v>
+        <v>0.7897262243675119</v>
       </c>
       <c r="U11">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0</v>
       </c>
       <c r="W11">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>14.09563299670221</v>
+        <v>12.31871246642296</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08286412166735722</v>
+        <v>0.08292412166735723</v>
       </c>
       <c r="C12">
-        <v>361.0375486150899</v>
+        <v>357.0302348234286</v>
       </c>
       <c r="D12">
-        <v>385.04754861509</v>
+        <v>384.4252348234286</v>
       </c>
       <c r="E12">
-        <v>-118.75</v>
+        <v>-115.365</v>
       </c>
       <c r="F12">
-        <v>33.85</v>
+        <v>37.235</v>
       </c>
       <c r="G12">
         <v>9.84</v>
@@ -2265,28 +2265,28 @@
         <v>21.6</v>
       </c>
       <c r="M12">
-        <v>1.75343</v>
+        <v>1.928773</v>
       </c>
       <c r="N12">
-        <v>19.84657</v>
+        <v>19.671227</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>19.84657</v>
+        <v>19.671227</v>
       </c>
       <c r="Q12">
-        <v>28.24657</v>
+        <v>28.071227</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08631569074150802</v>
+        <v>0.0867709232217497</v>
       </c>
       <c r="T12">
-        <v>0.7897262243675119</v>
+        <v>0.7985995527311919</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>12.31871246642295</v>
+        <v>11.19882951492996</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08292412166735723</v>
+        <v>0.08298412166735723</v>
       </c>
       <c r="C13">
-        <v>357.0302348234286</v>
+        <v>353.024929352837</v>
       </c>
       <c r="D13">
-        <v>384.4252348234286</v>
+        <v>383.804929352837</v>
       </c>
       <c r="E13">
-        <v>-115.365</v>
+        <v>-111.98</v>
       </c>
       <c r="F13">
-        <v>37.235</v>
+        <v>40.62</v>
       </c>
       <c r="G13">
         <v>9.84</v>
@@ -2347,28 +2347,28 @@
         <v>21.6</v>
       </c>
       <c r="M13">
-        <v>1.928773</v>
+        <v>2.104116</v>
       </c>
       <c r="N13">
-        <v>19.671227</v>
+        <v>19.495884</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13">
-        <v>19.671227</v>
+        <v>19.495884</v>
       </c>
       <c r="Q13">
-        <v>28.071227</v>
+        <v>27.895884</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0867709232217497</v>
+        <v>0.08723650189472412</v>
       </c>
       <c r="T13">
-        <v>0.7985995527311919</v>
+        <v>0.8076745476485917</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.19882951492996</v>
+        <v>10.26559372201913</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08298412166735723</v>
+        <v>0.08326512166735722</v>
       </c>
       <c r="C14">
-        <v>353.024929352837</v>
+        <v>346.7612736766135</v>
       </c>
       <c r="D14">
-        <v>383.804929352837</v>
+        <v>380.9262736766135</v>
       </c>
       <c r="E14">
-        <v>-111.98</v>
+        <v>-108.595</v>
       </c>
       <c r="F14">
-        <v>40.62</v>
+        <v>44.005</v>
       </c>
       <c r="G14">
         <v>9.84</v>
@@ -2429,45 +2429,45 @@
         <v>21.6</v>
       </c>
       <c r="M14">
-        <v>2.104116</v>
+        <v>2.3542675</v>
       </c>
       <c r="N14">
-        <v>19.495884</v>
+        <v>19.2457325</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14">
-        <v>19.495884</v>
+        <v>19.2457325</v>
       </c>
       <c r="Q14">
-        <v>27.895884</v>
+        <v>27.6457325</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08723650189472412</v>
+        <v>0.08771278352569796</v>
       </c>
       <c r="T14">
-        <v>0.8076745476485917</v>
+        <v>0.8169581631388054</v>
       </c>
       <c r="U14">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V14">
         <v>0</v>
       </c>
       <c r="W14">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y14">
-        <v>10.26559372201913</v>
+        <v>9.174828263992941</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08326512166735722</v>
+        <v>0.08334212166735723</v>
       </c>
       <c r="C15">
-        <v>346.7612736766135</v>
+        <v>342.5949826421592</v>
       </c>
       <c r="D15">
-        <v>380.9262736766135</v>
+        <v>380.1449826421592</v>
       </c>
       <c r="E15">
-        <v>-108.595</v>
+        <v>-105.21</v>
       </c>
       <c r="F15">
-        <v>44.005</v>
+        <v>47.39000000000001</v>
       </c>
       <c r="G15">
         <v>9.84</v>
@@ -2511,28 +2511,28 @@
         <v>21.6</v>
       </c>
       <c r="M15">
-        <v>2.3542675</v>
+        <v>2.535365000000001</v>
       </c>
       <c r="N15">
-        <v>19.2457325</v>
+        <v>19.064635</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>19.2457325</v>
+        <v>19.064635</v>
       </c>
       <c r="Q15">
-        <v>27.6457325</v>
+        <v>27.464635</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08771278352569796</v>
+        <v>0.0882001414736712</v>
       </c>
       <c r="T15">
-        <v>0.8169581631388054</v>
+        <v>0.8264576766636753</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>9.174828263992941</v>
+        <v>8.519483387993445</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08334212166735723</v>
+        <v>0.08341912166735722</v>
       </c>
       <c r="C16">
-        <v>342.5949826421592</v>
+        <v>338.4318899497706</v>
       </c>
       <c r="D16">
-        <v>380.1449826421592</v>
+        <v>379.3668899497706</v>
       </c>
       <c r="E16">
-        <v>-105.21</v>
+        <v>-101.825</v>
       </c>
       <c r="F16">
-        <v>47.39000000000001</v>
+        <v>50.77500000000001</v>
       </c>
       <c r="G16">
         <v>9.84</v>
@@ -2593,28 +2593,28 @@
         <v>21.6</v>
       </c>
       <c r="M16">
-        <v>2.535365000000001</v>
+        <v>2.7164625</v>
       </c>
       <c r="N16">
-        <v>19.064635</v>
+        <v>18.8835375</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>19.064635</v>
+        <v>18.8835375</v>
       </c>
       <c r="Q16">
-        <v>27.464635</v>
+        <v>27.2835375</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0882001414736712</v>
+        <v>0.08869896666747909</v>
       </c>
       <c r="T16">
-        <v>0.8264576766636753</v>
+        <v>0.8361807081538362</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.519483387993445</v>
+        <v>7.951517828793881</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08341912166735722</v>
+        <v>0.08362412166735723</v>
       </c>
       <c r="C17">
-        <v>338.4318899497706</v>
+        <v>332.9907890011841</v>
       </c>
       <c r="D17">
-        <v>379.3668899497706</v>
+        <v>377.3107890011841</v>
       </c>
       <c r="E17">
-        <v>-101.825</v>
+        <v>-98.44</v>
       </c>
       <c r="F17">
-        <v>50.775</v>
+        <v>54.16</v>
       </c>
       <c r="G17">
         <v>9.84</v>
@@ -2675,45 +2675,45 @@
         <v>21.6</v>
       </c>
       <c r="M17">
-        <v>2.7164625</v>
+        <v>2.940888</v>
       </c>
       <c r="N17">
-        <v>18.8835375</v>
+        <v>18.659112</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17">
-        <v>18.8835375</v>
+        <v>18.659112</v>
       </c>
       <c r="Q17">
-        <v>27.2835375</v>
+        <v>27.059112</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08869896666747909</v>
+        <v>0.08920966865161575</v>
       </c>
       <c r="T17">
-        <v>0.8361807081538362</v>
+        <v>0.8461352403937628</v>
       </c>
       <c r="U17">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V17">
         <v>0</v>
       </c>
       <c r="W17">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y17">
-        <v>7.951517828793882</v>
+        <v>7.344720370173906</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08362412166735723</v>
+        <v>0.08370912166735724</v>
       </c>
       <c r="C18">
-        <v>332.9907890011841</v>
+        <v>328.7597810839729</v>
       </c>
       <c r="D18">
-        <v>377.3107890011841</v>
+        <v>376.464781083973</v>
       </c>
       <c r="E18">
-        <v>-98.44</v>
+        <v>-95.05499999999999</v>
       </c>
       <c r="F18">
-        <v>54.16</v>
+        <v>57.545</v>
       </c>
       <c r="G18">
         <v>9.84</v>
@@ -2757,28 +2757,28 @@
         <v>21.6</v>
       </c>
       <c r="M18">
-        <v>2.940888</v>
+        <v>3.1246935</v>
       </c>
       <c r="N18">
-        <v>18.659112</v>
+        <v>18.4753065</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18">
-        <v>18.659112</v>
+        <v>18.4753065</v>
       </c>
       <c r="Q18">
-        <v>27.059112</v>
+        <v>26.8753065</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08920966865161575</v>
+        <v>0.08973267670765932</v>
       </c>
       <c r="T18">
-        <v>0.8461352403937628</v>
+        <v>0.8563296408804347</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.344720370173906</v>
+        <v>6.912677995457795</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08370912166735724</v>
+        <v>0.08379412166735722</v>
       </c>
       <c r="C19">
-        <v>328.7597810839729</v>
+        <v>324.5325585245915</v>
       </c>
       <c r="D19">
-        <v>376.464781083973</v>
+        <v>375.6225585245915</v>
       </c>
       <c r="E19">
-        <v>-95.05499999999999</v>
+        <v>-91.66999999999999</v>
       </c>
       <c r="F19">
-        <v>57.545</v>
+        <v>60.93000000000001</v>
       </c>
       <c r="G19">
         <v>9.84</v>
@@ -2839,28 +2839,28 @@
         <v>21.6</v>
       </c>
       <c r="M19">
-        <v>3.1246935</v>
+        <v>3.308499</v>
       </c>
       <c r="N19">
-        <v>18.4753065</v>
+        <v>18.291501</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19">
-        <v>18.4753065</v>
+        <v>18.291501</v>
       </c>
       <c r="Q19">
-        <v>26.8753065</v>
+        <v>26.691501</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08973267670765932</v>
+        <v>0.09026844105775271</v>
       </c>
       <c r="T19">
-        <v>0.8563296408804347</v>
+        <v>0.8667726852814155</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.912677995457795</v>
+        <v>6.528640329043472</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08379412166735724</v>
+        <v>0.08387912166735723</v>
       </c>
       <c r="C20">
-        <v>324.5325585245913</v>
+        <v>320.3090959740763</v>
       </c>
       <c r="D20">
-        <v>375.6225585245913</v>
+        <v>374.7840959740763</v>
       </c>
       <c r="E20">
-        <v>-91.66999999999999</v>
+        <v>-88.285</v>
       </c>
       <c r="F20">
-        <v>60.93</v>
+        <v>64.315</v>
       </c>
       <c r="G20">
         <v>9.84</v>
@@ -2921,28 +2921,28 @@
         <v>21.6</v>
       </c>
       <c r="M20">
-        <v>3.308499</v>
+        <v>3.4923045</v>
       </c>
       <c r="N20">
-        <v>18.291501</v>
+        <v>18.1076955</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20">
-        <v>18.291501</v>
+        <v>18.1076955</v>
       </c>
       <c r="Q20">
-        <v>26.691501</v>
+        <v>26.5076955</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09026844105775271</v>
+        <v>0.09081743415723115</v>
       </c>
       <c r="T20">
-        <v>0.8667726852814155</v>
+        <v>0.8774735826305687</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.528640329043473</v>
+        <v>6.185027680146448</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08387912166735723</v>
+        <v>0.08416412166735723</v>
       </c>
       <c r="C21">
-        <v>320.3090959740763</v>
+        <v>314.139893893842</v>
       </c>
       <c r="D21">
-        <v>374.7840959740763</v>
+        <v>371.9998938938421</v>
       </c>
       <c r="E21">
-        <v>-88.285</v>
+        <v>-84.89999999999999</v>
       </c>
       <c r="F21">
-        <v>64.315</v>
+        <v>67.7</v>
       </c>
       <c r="G21">
         <v>9.84</v>
@@ -3003,45 +3003,45 @@
         <v>21.6</v>
       </c>
       <c r="M21">
-        <v>3.4923045</v>
+        <v>3.74381</v>
       </c>
       <c r="N21">
-        <v>18.1076955</v>
+        <v>17.85619</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21">
-        <v>18.1076955</v>
+        <v>17.85619</v>
       </c>
       <c r="Q21">
-        <v>26.5076955</v>
+        <v>26.25619</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09081743415723115</v>
+        <v>0.09138015208419653</v>
       </c>
       <c r="T21">
-        <v>0.8774735826305687</v>
+        <v>0.8884420024134509</v>
       </c>
       <c r="U21">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V21">
         <v>0</v>
       </c>
       <c r="W21">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y21">
-        <v>6.185027680146448</v>
+        <v>5.769523560223409</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08416412166735723</v>
+        <v>0.08425912166735723</v>
       </c>
       <c r="C22">
-        <v>314.139893893842</v>
+        <v>309.8359964154862</v>
       </c>
       <c r="D22">
-        <v>371.9998938938421</v>
+        <v>371.0809964154863</v>
       </c>
       <c r="E22">
-        <v>-84.89999999999999</v>
+        <v>-81.51499999999999</v>
       </c>
       <c r="F22">
-        <v>67.7</v>
+        <v>71.08500000000001</v>
       </c>
       <c r="G22">
         <v>9.84</v>
@@ -3085,28 +3085,28 @@
         <v>21.6</v>
       </c>
       <c r="M22">
-        <v>3.74381</v>
+        <v>3.931000500000001</v>
       </c>
       <c r="N22">
-        <v>17.85619</v>
+        <v>17.6689995</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>17.85619</v>
+        <v>17.6689995</v>
       </c>
       <c r="Q22">
-        <v>26.25619</v>
+        <v>26.0689995</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09138015208419653</v>
+        <v>0.0919571160346294</v>
       </c>
       <c r="T22">
-        <v>0.8884420024134509</v>
+        <v>0.8996881037098238</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.769523560223409</v>
+        <v>5.494784343069913</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08425912166735723</v>
+        <v>0.08435412166735723</v>
       </c>
       <c r="C23">
-        <v>309.8359964154862</v>
+        <v>305.5366273899479</v>
       </c>
       <c r="D23">
-        <v>371.0809964154863</v>
+        <v>370.1666273899478</v>
       </c>
       <c r="E23">
-        <v>-81.515</v>
+        <v>-78.13</v>
       </c>
       <c r="F23">
-        <v>71.08499999999999</v>
+        <v>74.47</v>
       </c>
       <c r="G23">
         <v>9.84</v>
@@ -3167,28 +3167,28 @@
         <v>21.6</v>
       </c>
       <c r="M23">
-        <v>3.9310005</v>
+        <v>4.118191</v>
       </c>
       <c r="N23">
-        <v>17.6689995</v>
+        <v>17.481809</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>17.6689995</v>
+        <v>17.481809</v>
       </c>
       <c r="Q23">
-        <v>26.0689995</v>
+        <v>25.881809</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0919571160346294</v>
+        <v>0.09254887393250927</v>
       </c>
       <c r="T23">
-        <v>0.8996881037098238</v>
+        <v>0.9112225665778984</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.494784343069914</v>
+        <v>5.245021418384917</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08435412166735723</v>
+        <v>0.08444912166735721</v>
       </c>
       <c r="C24">
-        <v>305.5366273899479</v>
+        <v>301.2417534242546</v>
       </c>
       <c r="D24">
-        <v>370.1666273899478</v>
+        <v>369.2567534242546</v>
       </c>
       <c r="E24">
-        <v>-78.13</v>
+        <v>-74.74499999999999</v>
       </c>
       <c r="F24">
-        <v>74.47</v>
+        <v>77.855</v>
       </c>
       <c r="G24">
         <v>9.84</v>
@@ -3249,28 +3249,28 @@
         <v>21.6</v>
       </c>
       <c r="M24">
-        <v>4.118191</v>
+        <v>4.3053815</v>
       </c>
       <c r="N24">
-        <v>17.481809</v>
+        <v>17.2946185</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
       <c r="P24">
-        <v>17.481809</v>
+        <v>17.2946185</v>
       </c>
       <c r="Q24">
-        <v>25.881809</v>
+        <v>25.6946185</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09254887393250927</v>
+        <v>0.09315600216539899</v>
       </c>
       <c r="T24">
-        <v>0.9112225665778984</v>
+        <v>0.9230566258841049</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.245021418384917</v>
+        <v>5.016977008889921</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08444912166735721</v>
+        <v>0.08454412166735724</v>
       </c>
       <c r="C25">
-        <v>301.2417534242546</v>
+        <v>296.9513414529498</v>
       </c>
       <c r="D25">
-        <v>369.2567534242546</v>
+        <v>368.3513414529498</v>
       </c>
       <c r="E25">
-        <v>-74.74499999999999</v>
+        <v>-71.35999999999999</v>
       </c>
       <c r="F25">
-        <v>77.855</v>
+        <v>81.24000000000001</v>
       </c>
       <c r="G25">
         <v>9.84</v>
@@ -3331,28 +3331,28 @@
         <v>21.6</v>
       </c>
       <c r="M25">
-        <v>4.3053815</v>
+        <v>4.492572000000001</v>
       </c>
       <c r="N25">
-        <v>17.2946185</v>
+        <v>17.107428</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>17.2946185</v>
+        <v>17.107428</v>
       </c>
       <c r="Q25">
-        <v>25.6946185</v>
+        <v>25.507428</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09315600216539899</v>
+        <v>0.09377910745704898</v>
       </c>
       <c r="T25">
-        <v>0.9230566258841049</v>
+        <v>0.9352021078036327</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.016977008889921</v>
+        <v>4.807936300186173</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08454412166735724</v>
+        <v>0.08463912166735722</v>
       </c>
       <c r="C26">
-        <v>296.9513414529498</v>
+        <v>292.6653587340889</v>
       </c>
       <c r="D26">
-        <v>368.3513414529498</v>
+        <v>367.4503587340889</v>
       </c>
       <c r="E26">
-        <v>-71.36</v>
+        <v>-67.97499999999999</v>
       </c>
       <c r="F26">
-        <v>81.23999999999999</v>
+        <v>84.625</v>
       </c>
       <c r="G26">
         <v>9.84</v>
@@ -3413,28 +3413,28 @@
         <v>21.6</v>
       </c>
       <c r="M26">
-        <v>4.492572</v>
+        <v>4.6797625</v>
       </c>
       <c r="N26">
-        <v>17.107428</v>
+        <v>16.9202375</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
       <c r="P26">
-        <v>17.107428</v>
+        <v>16.9202375</v>
       </c>
       <c r="Q26">
-        <v>25.507428</v>
+        <v>25.3202375</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09377910745704898</v>
+        <v>0.09441882888980963</v>
       </c>
       <c r="T26">
-        <v>0.9352021078036327</v>
+        <v>0.9476714692410143</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.807936300186174</v>
+        <v>4.615618848178728</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08463912166735722</v>
+        <v>0.08538412166735722</v>
       </c>
       <c r="C27">
-        <v>292.6653587340889</v>
+        <v>282.3646939239072</v>
       </c>
       <c r="D27">
-        <v>367.4503587340889</v>
+        <v>360.5346939239072</v>
       </c>
       <c r="E27">
-        <v>-67.97499999999999</v>
+        <v>-64.58999999999999</v>
       </c>
       <c r="F27">
-        <v>84.625</v>
+        <v>88.01000000000001</v>
       </c>
       <c r="G27">
         <v>9.84</v>
@@ -3495,45 +3495,45 @@
         <v>21.6</v>
       </c>
       <c r="M27">
-        <v>4.6797625</v>
+        <v>5.086978</v>
       </c>
       <c r="N27">
-        <v>16.9202375</v>
+        <v>16.513022</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27">
-        <v>16.9202375</v>
+        <v>16.513022</v>
       </c>
       <c r="Q27">
-        <v>25.3202375</v>
+        <v>24.913022</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09441882888980963</v>
+        <v>0.09507584009102327</v>
       </c>
       <c r="T27">
-        <v>0.9476714692410143</v>
+        <v>0.9604778404469739</v>
       </c>
       <c r="U27">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V27">
         <v>0</v>
       </c>
       <c r="W27">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y27">
-        <v>4.615618848178728</v>
+        <v>4.246135918024414</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08538412166735722</v>
+        <v>0.08550412166735724</v>
       </c>
       <c r="C28">
-        <v>282.3646939239072</v>
+        <v>277.890029640855</v>
       </c>
       <c r="D28">
-        <v>360.5346939239072</v>
+        <v>359.4450296408551</v>
       </c>
       <c r="E28">
-        <v>-64.58999999999999</v>
+        <v>-61.20499999999998</v>
       </c>
       <c r="F28">
-        <v>88.01000000000001</v>
+        <v>91.39500000000001</v>
       </c>
       <c r="G28">
         <v>9.84</v>
@@ -3577,28 +3577,28 @@
         <v>21.6</v>
       </c>
       <c r="M28">
-        <v>5.086978</v>
+        <v>5.282631000000001</v>
       </c>
       <c r="N28">
-        <v>16.513022</v>
+        <v>16.317369</v>
       </c>
       <c r="O28">
         <v>0</v>
       </c>
       <c r="P28">
-        <v>16.513022</v>
+        <v>16.317369</v>
       </c>
       <c r="Q28">
-        <v>24.913022</v>
+        <v>24.717369</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09507584009102327</v>
+        <v>0.0957508515991195</v>
       </c>
       <c r="T28">
-        <v>0.9604778404469739</v>
+        <v>0.9736350711380285</v>
       </c>
       <c r="U28">
         <v>0.0578</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.246135918024414</v>
+        <v>4.08887162476425</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08550412166735724</v>
+        <v>0.08660412166735723</v>
       </c>
       <c r="C29">
-        <v>277.890029640855</v>
+        <v>264.8150886141071</v>
       </c>
       <c r="D29">
-        <v>359.4450296408551</v>
+        <v>349.7550886141072</v>
       </c>
       <c r="E29">
-        <v>-61.20499999999998</v>
+        <v>-57.81999999999998</v>
       </c>
       <c r="F29">
-        <v>91.39500000000001</v>
+        <v>94.78000000000002</v>
       </c>
       <c r="G29">
         <v>9.84</v>
@@ -3659,45 +3659,45 @@
         <v>21.6</v>
       </c>
       <c r="M29">
-        <v>5.282631000000001</v>
+        <v>5.810014000000001</v>
       </c>
       <c r="N29">
-        <v>16.317369</v>
+        <v>15.789986</v>
       </c>
       <c r="O29">
         <v>0</v>
       </c>
       <c r="P29">
-        <v>16.317369</v>
+        <v>15.789986</v>
       </c>
       <c r="Q29">
-        <v>24.717369</v>
+        <v>24.189986</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.0957508515991195</v>
+        <v>0.09644461342688504</v>
       </c>
       <c r="T29">
-        <v>0.9736350711380285</v>
+        <v>0.98715778045939</v>
       </c>
       <c r="U29">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V29">
         <v>0</v>
       </c>
       <c r="W29">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>4.08887162476425</v>
+        <v>3.717719096718183</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08660412166735723</v>
+        <v>0.08675912166735723</v>
       </c>
       <c r="C30">
-        <v>264.8150886141071</v>
+        <v>260.1065241300964</v>
       </c>
       <c r="D30">
-        <v>349.7550886141072</v>
+        <v>348.4315241300965</v>
       </c>
       <c r="E30">
-        <v>-57.81999999999998</v>
+        <v>-54.43499999999999</v>
       </c>
       <c r="F30">
-        <v>94.78000000000002</v>
+        <v>98.16500000000001</v>
       </c>
       <c r="G30">
         <v>9.84</v>
@@ -3741,28 +3741,28 @@
         <v>21.6</v>
       </c>
       <c r="M30">
-        <v>5.810014000000001</v>
+        <v>6.017514500000001</v>
       </c>
       <c r="N30">
-        <v>15.789986</v>
+        <v>15.5824855</v>
       </c>
       <c r="O30">
         <v>0</v>
       </c>
       <c r="P30">
-        <v>15.789986</v>
+        <v>15.5824855</v>
       </c>
       <c r="Q30">
-        <v>24.189986</v>
+        <v>23.9824855</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09644461342688504</v>
+        <v>0.09715791784134822</v>
       </c>
       <c r="T30">
-        <v>0.98715778045939</v>
+        <v>1.001061411170086</v>
       </c>
       <c r="U30">
         <v>0.0613</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.717719096718183</v>
+        <v>3.589521886486522</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08675912166735722</v>
+        <v>0.08775412166735722</v>
       </c>
       <c r="C31">
-        <v>260.1065241300967</v>
+        <v>248.4579888031447</v>
       </c>
       <c r="D31">
-        <v>348.4315241300966</v>
+        <v>340.1679888031447</v>
       </c>
       <c r="E31">
-        <v>-54.435</v>
+        <v>-51.05</v>
       </c>
       <c r="F31">
-        <v>98.16499999999999</v>
+        <v>101.55</v>
       </c>
       <c r="G31">
         <v>9.84</v>
@@ -3823,45 +3823,45 @@
         <v>21.6</v>
       </c>
       <c r="M31">
-        <v>6.0175145</v>
+        <v>6.509355</v>
       </c>
       <c r="N31">
-        <v>15.5824855</v>
+        <v>15.090645</v>
       </c>
       <c r="O31">
         <v>0</v>
       </c>
       <c r="P31">
-        <v>15.5824855</v>
+        <v>15.090645</v>
       </c>
       <c r="Q31">
-        <v>23.9824855</v>
+        <v>23.490645</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.0971579178413482</v>
+        <v>0.09789160238193889</v>
       </c>
       <c r="T31">
-        <v>1.001061411170086</v>
+        <v>1.015362288472515</v>
       </c>
       <c r="U31">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V31">
         <v>0</v>
       </c>
       <c r="W31">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y31">
-        <v>3.589521886486522</v>
+        <v>3.318301122000567</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08775412166735722</v>
+        <v>0.08793712166735723</v>
       </c>
       <c r="C32">
-        <v>248.4579888031447</v>
+        <v>243.5956514937193</v>
       </c>
       <c r="D32">
-        <v>340.1679888031447</v>
+        <v>338.6906514937194</v>
       </c>
       <c r="E32">
-        <v>-51.05</v>
+        <v>-47.66499999999999</v>
       </c>
       <c r="F32">
-        <v>101.55</v>
+        <v>104.935</v>
       </c>
       <c r="G32">
         <v>9.84</v>
@@ -3905,28 +3905,28 @@
         <v>21.6</v>
       </c>
       <c r="M32">
-        <v>6.509355</v>
+        <v>6.726333500000001</v>
       </c>
       <c r="N32">
-        <v>15.090645</v>
+        <v>14.8736665</v>
       </c>
       <c r="O32">
         <v>0</v>
       </c>
       <c r="P32">
-        <v>15.090645</v>
+        <v>14.8736665</v>
       </c>
       <c r="Q32">
-        <v>23.490645</v>
+        <v>23.2736665</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09789160238193889</v>
+        <v>0.09864655314109744</v>
       </c>
       <c r="T32">
-        <v>1.015362288472515</v>
+        <v>1.030077683957624</v>
       </c>
       <c r="U32">
         <v>0.0641</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.318301122000567</v>
+        <v>3.211259150323129</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08793712166735723</v>
+        <v>0.08812012166735722</v>
       </c>
       <c r="C33">
-        <v>243.5956514937193</v>
+        <v>238.7460907414956</v>
       </c>
       <c r="D33">
-        <v>338.6906514937194</v>
+        <v>337.2260907414956</v>
       </c>
       <c r="E33">
-        <v>-47.66499999999999</v>
+        <v>-44.27999999999999</v>
       </c>
       <c r="F33">
-        <v>104.935</v>
+        <v>108.32</v>
       </c>
       <c r="G33">
         <v>9.84</v>
@@ -3987,28 +3987,28 @@
         <v>21.6</v>
       </c>
       <c r="M33">
-        <v>6.726333500000001</v>
+        <v>6.943312000000001</v>
       </c>
       <c r="N33">
-        <v>14.8736665</v>
+        <v>14.656688</v>
       </c>
       <c r="O33">
         <v>0</v>
       </c>
       <c r="P33">
-        <v>14.8736665</v>
+        <v>14.656688</v>
       </c>
       <c r="Q33">
-        <v>23.2736665</v>
+        <v>23.056688</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09864655314109744</v>
+        <v>0.09942370833434887</v>
       </c>
       <c r="T33">
-        <v>1.030077683957624</v>
+        <v>1.045225885192295</v>
       </c>
       <c r="U33">
         <v>0.0641</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.211259150323129</v>
+        <v>3.110907301875531</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08812012166735722</v>
+        <v>0.08830312166735724</v>
       </c>
       <c r="C34">
-        <v>238.7460907414956</v>
+        <v>233.909141515538</v>
       </c>
       <c r="D34">
-        <v>337.2260907414956</v>
+        <v>335.774141515538</v>
       </c>
       <c r="E34">
-        <v>-44.27999999999999</v>
+        <v>-40.895</v>
       </c>
       <c r="F34">
-        <v>108.32</v>
+        <v>111.705</v>
       </c>
       <c r="G34">
         <v>9.84</v>
@@ -4069,28 +4069,28 @@
         <v>21.6</v>
       </c>
       <c r="M34">
-        <v>6.943312000000001</v>
+        <v>7.1602905</v>
       </c>
       <c r="N34">
-        <v>14.656688</v>
+        <v>14.4397095</v>
       </c>
       <c r="O34">
         <v>0</v>
       </c>
       <c r="P34">
-        <v>14.656688</v>
+        <v>14.4397095</v>
       </c>
       <c r="Q34">
-        <v>23.056688</v>
+        <v>22.8397095</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09942370833434887</v>
+        <v>0.1002240621900854</v>
       </c>
       <c r="T34">
-        <v>1.045225885192295</v>
+        <v>1.060826271538449</v>
       </c>
       <c r="U34">
         <v>0.0641</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.110907301875531</v>
+        <v>3.016637383636879</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08830312166735724</v>
+        <v>0.09113812166735721</v>
       </c>
       <c r="C35">
-        <v>233.909141515538</v>
+        <v>209.5281307372196</v>
       </c>
       <c r="D35">
-        <v>335.774141515538</v>
+        <v>314.7781307372197</v>
       </c>
       <c r="E35">
-        <v>-40.895</v>
+        <v>-37.50999999999999</v>
       </c>
       <c r="F35">
-        <v>111.705</v>
+        <v>115.09</v>
       </c>
       <c r="G35">
         <v>9.84</v>
@@ -4151,45 +4151,45 @@
         <v>21.6</v>
       </c>
       <c r="M35">
-        <v>7.1602905</v>
+        <v>8.274971000000001</v>
       </c>
       <c r="N35">
-        <v>14.4397095</v>
+        <v>13.325029</v>
       </c>
       <c r="O35">
         <v>0</v>
       </c>
       <c r="P35">
-        <v>14.4397095</v>
+        <v>13.325029</v>
       </c>
       <c r="Q35">
-        <v>22.8397095</v>
+        <v>21.725029</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1002240621900854</v>
+        <v>0.1010486691929655</v>
       </c>
       <c r="T35">
-        <v>1.060826271538449</v>
+        <v>1.076899396864789</v>
       </c>
       <c r="U35">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V35">
         <v>0</v>
       </c>
       <c r="W35">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>3.016637383636879</v>
+        <v>2.61028105113601</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09113812166735721</v>
+        <v>0.09139912166735724</v>
       </c>
       <c r="C36">
-        <v>209.5281307372196</v>
+        <v>204.3414054162419</v>
       </c>
       <c r="D36">
-        <v>314.7781307372197</v>
+        <v>312.9764054162419</v>
       </c>
       <c r="E36">
-        <v>-37.50999999999999</v>
+        <v>-34.12499999999999</v>
       </c>
       <c r="F36">
-        <v>115.09</v>
+        <v>118.475</v>
       </c>
       <c r="G36">
         <v>9.84</v>
@@ -4233,28 +4233,28 @@
         <v>21.6</v>
       </c>
       <c r="M36">
-        <v>8.274971000000001</v>
+        <v>8.518352500000001</v>
       </c>
       <c r="N36">
-        <v>13.325029</v>
+        <v>13.0816475</v>
       </c>
       <c r="O36">
         <v>0</v>
       </c>
       <c r="P36">
-        <v>13.325029</v>
+        <v>13.0816475</v>
       </c>
       <c r="Q36">
-        <v>21.725029</v>
+        <v>21.4816475</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1010486691929655</v>
+        <v>0.1018986487190111</v>
       </c>
       <c r="T36">
-        <v>1.076899396864789</v>
+        <v>1.093467079893478</v>
       </c>
       <c r="U36">
         <v>0.07190000000000001</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.61028105113601</v>
+        <v>2.535701592532124</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09139912166735724</v>
+        <v>0.09306412166735722</v>
       </c>
       <c r="C37">
-        <v>204.3414054162419</v>
+        <v>189.9310082093381</v>
       </c>
       <c r="D37">
-        <v>312.9764054162419</v>
+        <v>301.9510082093382</v>
       </c>
       <c r="E37">
-        <v>-34.12499999999999</v>
+        <v>-30.73999999999998</v>
       </c>
       <c r="F37">
-        <v>118.475</v>
+        <v>121.86</v>
       </c>
       <c r="G37">
         <v>9.84</v>
@@ -4315,45 +4315,45 @@
         <v>21.6</v>
       </c>
       <c r="M37">
-        <v>8.518352500000001</v>
+        <v>9.236988000000002</v>
       </c>
       <c r="N37">
-        <v>13.0816475</v>
+        <v>12.363012</v>
       </c>
       <c r="O37">
         <v>0</v>
       </c>
       <c r="P37">
-        <v>13.0816475</v>
+        <v>12.363012</v>
       </c>
       <c r="Q37">
-        <v>21.4816475</v>
+        <v>20.763012</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1018986487190111</v>
+        <v>0.1027751901052457</v>
       </c>
       <c r="T37">
-        <v>1.093467079893478</v>
+        <v>1.110552503016814</v>
       </c>
       <c r="U37">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V37">
         <v>0</v>
       </c>
       <c r="W37">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y37">
-        <v>2.535701592532124</v>
+        <v>2.338424603344726</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09306412166735722</v>
+        <v>0.09336412166735723</v>
       </c>
       <c r="C38">
-        <v>189.9310082093381</v>
+        <v>184.6415201354004</v>
       </c>
       <c r="D38">
-        <v>301.9510082093382</v>
+        <v>300.0465201354004</v>
       </c>
       <c r="E38">
-        <v>-30.73999999999999</v>
+        <v>-27.35499999999999</v>
       </c>
       <c r="F38">
-        <v>121.86</v>
+        <v>125.245</v>
       </c>
       <c r="G38">
         <v>9.84</v>
@@ -4397,28 +4397,28 @@
         <v>21.6</v>
       </c>
       <c r="M38">
-        <v>9.236988</v>
+        <v>9.493571000000001</v>
       </c>
       <c r="N38">
-        <v>12.363012</v>
+        <v>12.106429</v>
       </c>
       <c r="O38">
         <v>0</v>
       </c>
       <c r="P38">
-        <v>12.363012</v>
+        <v>12.106429</v>
       </c>
       <c r="Q38">
-        <v>20.763012</v>
+        <v>20.506429</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1027751901052457</v>
+        <v>0.1036795582021543</v>
       </c>
       <c r="T38">
-        <v>1.110552503016814</v>
+        <v>1.128180320525017</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.338424603344727</v>
+        <v>2.275223938389463</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09336412166735723</v>
+        <v>0.09366412166735721</v>
       </c>
       <c r="C39">
-        <v>184.6415201354004</v>
+        <v>179.3759057439741</v>
       </c>
       <c r="D39">
-        <v>300.0465201354004</v>
+        <v>298.1659057439741</v>
       </c>
       <c r="E39">
-        <v>-27.35499999999999</v>
+        <v>-23.97</v>
       </c>
       <c r="F39">
-        <v>125.245</v>
+        <v>128.63</v>
       </c>
       <c r="G39">
         <v>9.84</v>
@@ -4479,28 +4479,28 @@
         <v>21.6</v>
       </c>
       <c r="M39">
-        <v>9.493571000000001</v>
+        <v>9.750154</v>
       </c>
       <c r="N39">
-        <v>12.106429</v>
+        <v>11.849846</v>
       </c>
       <c r="O39">
         <v>0</v>
       </c>
       <c r="P39">
-        <v>12.106429</v>
+        <v>11.849846</v>
       </c>
       <c r="Q39">
-        <v>20.506429</v>
+        <v>20.249846</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1036795582021543</v>
+        <v>0.1046130994634794</v>
       </c>
       <c r="T39">
-        <v>1.128180320525017</v>
+        <v>1.146376777307679</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.275223938389463</v>
+        <v>2.21534962422132</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09366412166735721</v>
+        <v>0.09396412166735724</v>
       </c>
       <c r="C40">
-        <v>179.3759057439741</v>
+        <v>174.1337189288385</v>
       </c>
       <c r="D40">
-        <v>298.1659057439741</v>
+        <v>296.3087189288386</v>
       </c>
       <c r="E40">
-        <v>-23.97</v>
+        <v>-20.58499999999998</v>
       </c>
       <c r="F40">
-        <v>128.63</v>
+        <v>132.015</v>
       </c>
       <c r="G40">
         <v>9.84</v>
@@ -4561,28 +4561,28 @@
         <v>21.6</v>
       </c>
       <c r="M40">
-        <v>9.750154</v>
+        <v>10.006737</v>
       </c>
       <c r="N40">
-        <v>11.849846</v>
+        <v>11.593263</v>
       </c>
       <c r="O40">
         <v>0</v>
       </c>
       <c r="P40">
-        <v>11.849846</v>
+        <v>11.593263</v>
       </c>
       <c r="Q40">
-        <v>20.249846</v>
+        <v>19.993263</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1046130994634794</v>
+        <v>0.1055772486350119</v>
       </c>
       <c r="T40">
-        <v>1.146376777307679</v>
+        <v>1.165169839230755</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.21534962422132</v>
+        <v>2.158545787702824</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09396412166735724</v>
+        <v>0.09426412166735723</v>
       </c>
       <c r="C41">
-        <v>174.1337189288385</v>
+        <v>168.9145246296252</v>
       </c>
       <c r="D41">
-        <v>296.3087189288386</v>
+        <v>294.4745246296252</v>
       </c>
       <c r="E41">
-        <v>-20.58499999999998</v>
+        <v>-17.19999999999999</v>
       </c>
       <c r="F41">
-        <v>132.015</v>
+        <v>135.4</v>
       </c>
       <c r="G41">
         <v>9.84</v>
@@ -4643,28 +4643,28 @@
         <v>21.6</v>
       </c>
       <c r="M41">
-        <v>10.006737</v>
+        <v>10.26332</v>
       </c>
       <c r="N41">
-        <v>11.593263</v>
+        <v>11.33668</v>
       </c>
       <c r="O41">
         <v>0</v>
       </c>
       <c r="P41">
-        <v>11.593263</v>
+        <v>11.33668</v>
       </c>
       <c r="Q41">
-        <v>19.993263</v>
+        <v>19.73668</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1055772486350119</v>
+        <v>0.1065735361122621</v>
       </c>
       <c r="T41">
-        <v>1.165169839230755</v>
+        <v>1.184589336551268</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.158545787702824</v>
+        <v>2.104582143010254</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09426412166735723</v>
+        <v>0.09456412166735723</v>
       </c>
       <c r="C42">
-        <v>168.9145246296252</v>
+        <v>163.7178984920417</v>
       </c>
       <c r="D42">
-        <v>294.4745246296252</v>
+        <v>292.6628984920417</v>
       </c>
       <c r="E42">
-        <v>-17.19999999999999</v>
+        <v>-13.815</v>
       </c>
       <c r="F42">
-        <v>135.4</v>
+        <v>138.785</v>
       </c>
       <c r="G42">
         <v>9.84</v>
@@ -4725,28 +4725,28 @@
         <v>21.6</v>
       </c>
       <c r="M42">
-        <v>10.26332</v>
+        <v>10.519903</v>
       </c>
       <c r="N42">
-        <v>11.33668</v>
+        <v>11.080097</v>
       </c>
       <c r="O42">
         <v>0</v>
       </c>
       <c r="P42">
-        <v>11.33668</v>
+        <v>11.080097</v>
       </c>
       <c r="Q42">
-        <v>19.73668</v>
+        <v>19.480097</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1065735361122621</v>
+        <v>0.1076035960463682</v>
       </c>
       <c r="T42">
-        <v>1.184589336551268</v>
+        <v>1.204667121916544</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.104582143010254</v>
+        <v>2.053250871229516</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09456412166735723</v>
+        <v>0.09486412166735722</v>
       </c>
       <c r="C43">
-        <v>163.7178984920417</v>
+        <v>158.5434265405642</v>
       </c>
       <c r="D43">
-        <v>292.6628984920417</v>
+        <v>290.8734265405643</v>
       </c>
       <c r="E43">
-        <v>-13.815</v>
+        <v>-10.42999999999998</v>
       </c>
       <c r="F43">
-        <v>138.785</v>
+        <v>142.17</v>
       </c>
       <c r="G43">
         <v>9.84</v>
@@ -4807,28 +4807,28 @@
         <v>21.6</v>
       </c>
       <c r="M43">
-        <v>10.519903</v>
+        <v>10.776486</v>
       </c>
       <c r="N43">
-        <v>11.080097</v>
+        <v>10.823514</v>
       </c>
       <c r="O43">
         <v>0</v>
       </c>
       <c r="P43">
-        <v>11.080097</v>
+        <v>10.823514</v>
       </c>
       <c r="Q43">
-        <v>19.480097</v>
+        <v>19.223514</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1076035960463682</v>
+        <v>0.1086691752885469</v>
       </c>
       <c r="T43">
-        <v>1.204667121916544</v>
+        <v>1.225437244708208</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.053250871229516</v>
+        <v>2.004363945724051</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09486412166735723</v>
+        <v>0.1012701216673572</v>
       </c>
       <c r="C44">
-        <v>158.5434265405642</v>
+        <v>121.5667358355593</v>
       </c>
       <c r="D44">
-        <v>290.8734265405642</v>
+        <v>257.2817358355593</v>
       </c>
       <c r="E44">
-        <v>-10.43000000000001</v>
+        <v>-7.044999999999987</v>
       </c>
       <c r="F44">
-        <v>142.17</v>
+        <v>145.555</v>
       </c>
       <c r="G44">
         <v>9.84</v>
@@ -4889,45 +4889,45 @@
         <v>21.6</v>
       </c>
       <c r="M44">
-        <v>10.776486</v>
+        <v>13.09995</v>
       </c>
       <c r="N44">
-        <v>10.823514</v>
+        <v>8.500050000000002</v>
       </c>
       <c r="O44">
         <v>0</v>
       </c>
       <c r="P44">
-        <v>10.823514</v>
+        <v>8.500050000000002</v>
       </c>
       <c r="Q44">
-        <v>19.223514</v>
+        <v>16.90005</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1086691752885469</v>
+        <v>0.1097721432760653</v>
       </c>
       <c r="T44">
-        <v>1.225437244708208</v>
+        <v>1.246936143738177</v>
       </c>
       <c r="U44">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V44">
         <v>0</v>
       </c>
       <c r="W44">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.004363945724052</v>
+        <v>1.648861255195631</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1012701216673572</v>
+        <v>0.1017121216673572</v>
       </c>
       <c r="C45">
-        <v>121.5667358355593</v>
+        <v>116.1478561713986</v>
       </c>
       <c r="D45">
-        <v>257.2817358355593</v>
+        <v>255.2478561713986</v>
       </c>
       <c r="E45">
-        <v>-7.044999999999987</v>
+        <v>-3.659999999999997</v>
       </c>
       <c r="F45">
-        <v>145.555</v>
+        <v>148.94</v>
       </c>
       <c r="G45">
         <v>9.84</v>
@@ -4971,28 +4971,28 @@
         <v>21.6</v>
       </c>
       <c r="M45">
-        <v>13.09995</v>
+        <v>13.4046</v>
       </c>
       <c r="N45">
-        <v>8.500050000000002</v>
+        <v>8.195400000000003</v>
       </c>
       <c r="O45">
         <v>0</v>
       </c>
       <c r="P45">
-        <v>8.500050000000002</v>
+        <v>8.195400000000003</v>
       </c>
       <c r="Q45">
-        <v>16.90005</v>
+        <v>16.59540000000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1097721432760653</v>
+        <v>0.1109145029774236</v>
       </c>
       <c r="T45">
-        <v>1.246936143738177</v>
+        <v>1.269202860590644</v>
       </c>
       <c r="U45">
         <v>0.09</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.648861255195631</v>
+        <v>1.611387135759367</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1017121216673572</v>
+        <v>0.1021541216673572</v>
       </c>
       <c r="C46">
-        <v>116.1478561713986</v>
+        <v>110.7608809992239</v>
       </c>
       <c r="D46">
-        <v>255.2478561713986</v>
+        <v>253.2458809992239</v>
       </c>
       <c r="E46">
-        <v>-3.659999999999997</v>
+        <v>-0.2749999999999773</v>
       </c>
       <c r="F46">
-        <v>148.94</v>
+        <v>152.325</v>
       </c>
       <c r="G46">
         <v>9.84</v>
@@ -5053,28 +5053,28 @@
         <v>21.6</v>
       </c>
       <c r="M46">
-        <v>13.4046</v>
+        <v>13.70925</v>
       </c>
       <c r="N46">
-        <v>8.195400000000003</v>
+        <v>7.890750000000001</v>
       </c>
       <c r="O46">
         <v>0</v>
       </c>
       <c r="P46">
-        <v>8.195400000000003</v>
+        <v>7.890750000000001</v>
       </c>
       <c r="Q46">
-        <v>16.59540000000001</v>
+        <v>16.29075</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1109145029774236</v>
+        <v>0.1120984030315586</v>
       </c>
       <c r="T46">
-        <v>1.269202860590644</v>
+        <v>1.292279276237747</v>
       </c>
       <c r="U46">
         <v>0.09</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.611387135759367</v>
+        <v>1.575578532742491</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1021541216673572</v>
+        <v>0.1025961216673572</v>
       </c>
       <c r="C47">
-        <v>110.7608809992239</v>
+        <v>105.4050654555635</v>
       </c>
       <c r="D47">
-        <v>253.2458809992239</v>
+        <v>251.2750654555635</v>
       </c>
       <c r="E47">
-        <v>-0.2749999999999773</v>
+        <v>3.110000000000014</v>
       </c>
       <c r="F47">
-        <v>152.325</v>
+        <v>155.71</v>
       </c>
       <c r="G47">
         <v>9.84</v>
@@ -5135,28 +5135,28 @@
         <v>21.6</v>
       </c>
       <c r="M47">
-        <v>13.70925</v>
+        <v>14.0139</v>
       </c>
       <c r="N47">
-        <v>7.890750000000001</v>
+        <v>7.586100000000002</v>
       </c>
       <c r="O47">
         <v>0</v>
       </c>
       <c r="P47">
-        <v>7.890750000000001</v>
+        <v>7.586100000000002</v>
       </c>
       <c r="Q47">
-        <v>16.29075</v>
+        <v>15.9861</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1120984030315586</v>
+        <v>0.1133261512358467</v>
       </c>
       <c r="T47">
-        <v>1.292279276237747</v>
+        <v>1.316210373945853</v>
       </c>
       <c r="U47">
         <v>0.09</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.575578532742491</v>
+        <v>1.541326825508959</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1025961216673572</v>
+        <v>0.1030381216673572</v>
       </c>
       <c r="C48">
-        <v>105.4050654555635</v>
+        <v>100.0796876846644</v>
       </c>
       <c r="D48">
-        <v>251.2750654555635</v>
+        <v>249.3346876846644</v>
       </c>
       <c r="E48">
-        <v>3.110000000000014</v>
+        <v>6.495000000000005</v>
       </c>
       <c r="F48">
-        <v>155.71</v>
+        <v>159.095</v>
       </c>
       <c r="G48">
         <v>9.84</v>
@@ -5217,28 +5217,28 @@
         <v>21.6</v>
       </c>
       <c r="M48">
-        <v>14.0139</v>
+        <v>14.31855</v>
       </c>
       <c r="N48">
-        <v>7.586100000000002</v>
+        <v>7.281450000000001</v>
       </c>
       <c r="O48">
         <v>0</v>
       </c>
       <c r="P48">
-        <v>7.586100000000002</v>
+        <v>7.281450000000001</v>
       </c>
       <c r="Q48">
-        <v>15.9861</v>
+        <v>15.68145</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1133261512358467</v>
+        <v>0.1146002295610514</v>
       </c>
       <c r="T48">
-        <v>1.316210373945853</v>
+        <v>1.341044531944832</v>
       </c>
       <c r="U48">
         <v>0.09</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.541326825508959</v>
+        <v>1.508532637732173</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1030381216673572</v>
+        <v>0.1307441216673572</v>
       </c>
       <c r="C49">
-        <v>100.0796876846644</v>
+        <v>15.36985058712594</v>
       </c>
       <c r="D49">
-        <v>249.3346876846644</v>
+        <v>168.009850587126</v>
       </c>
       <c r="E49">
-        <v>6.495000000000005</v>
+        <v>9.880000000000024</v>
       </c>
       <c r="F49">
-        <v>159.095</v>
+        <v>162.48</v>
       </c>
       <c r="G49">
         <v>9.84</v>
@@ -5299,45 +5299,45 @@
         <v>21.6</v>
       </c>
       <c r="M49">
-        <v>14.31855</v>
+        <v>23.85206400000001</v>
       </c>
       <c r="N49">
-        <v>7.281450000000001</v>
+        <v>-2.252064000000004</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P49">
-        <v>7.281450000000001</v>
+        <v>-2.252064000000004</v>
       </c>
       <c r="Q49">
-        <v>15.68145</v>
+        <v>6.147935999999996</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1146002295610514</v>
+        <v>0.1159233108987639</v>
       </c>
       <c r="T49">
-        <v>1.341044531944832</v>
+        <v>1.366833849866848</v>
       </c>
       <c r="U49">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V49">
         <v>0</v>
       </c>
       <c r="W49">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y49">
-        <v>1.508532637732173</v>
+        <v>0.905582007494194</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1307441216673572</v>
+        <v>0.1317541216673572</v>
       </c>
       <c r="C50">
-        <v>15.36985058712605</v>
+        <v>10.01065847392289</v>
       </c>
       <c r="D50">
-        <v>168.009850587126</v>
+        <v>166.0356584739229</v>
       </c>
       <c r="E50">
-        <v>9.879999999999995</v>
+        <v>13.26500000000001</v>
       </c>
       <c r="F50">
-        <v>162.48</v>
+        <v>165.865</v>
       </c>
       <c r="G50">
         <v>9.84</v>
@@ -5381,28 +5381,28 @@
         <v>21.6</v>
       </c>
       <c r="M50">
-        <v>23.852064</v>
+        <v>24.348982</v>
       </c>
       <c r="N50">
-        <v>-2.252064000000001</v>
+        <v>-2.748982000000002</v>
       </c>
       <c r="O50">
         <v>-0</v>
       </c>
       <c r="P50">
-        <v>-2.252064000000001</v>
+        <v>-2.748982000000002</v>
       </c>
       <c r="Q50">
-        <v>6.147936</v>
+        <v>5.651017999999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1159233108987639</v>
+        <v>0.1172982777791318</v>
       </c>
       <c r="T50">
-        <v>1.366833849866848</v>
+        <v>1.393634513589727</v>
       </c>
       <c r="U50">
         <v>0.1468</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.9055820074941942</v>
+        <v>0.887100742035129</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1317541216673572</v>
+        <v>0.1327641216673572</v>
       </c>
       <c r="C51">
-        <v>10.01065847392289</v>
+        <v>4.697322835691409</v>
       </c>
       <c r="D51">
-        <v>166.0356584739229</v>
+        <v>164.1073228356914</v>
       </c>
       <c r="E51">
-        <v>13.26500000000001</v>
+        <v>16.65000000000001</v>
       </c>
       <c r="F51">
-        <v>165.865</v>
+        <v>169.25</v>
       </c>
       <c r="G51">
         <v>9.84</v>
@@ -5463,28 +5463,28 @@
         <v>21.6</v>
       </c>
       <c r="M51">
-        <v>24.348982</v>
+        <v>24.8459</v>
       </c>
       <c r="N51">
-        <v>-2.748982000000002</v>
+        <v>-3.245900000000002</v>
       </c>
       <c r="O51">
         <v>-0</v>
       </c>
       <c r="P51">
-        <v>-2.748982000000002</v>
+        <v>-3.245900000000002</v>
       </c>
       <c r="Q51">
-        <v>5.651017999999999</v>
+        <v>5.154099999999998</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1172982777791318</v>
+        <v>0.1187282433347145</v>
       </c>
       <c r="T51">
-        <v>1.393634513589727</v>
+        <v>1.421507203861522</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.887100742035129</v>
+        <v>0.8693587271944263</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1327641216673572</v>
+        <v>0.1337741216673572</v>
       </c>
       <c r="C52">
-        <v>4.697322835691409</v>
+        <v>-0.5717357138303498</v>
       </c>
       <c r="D52">
-        <v>164.1073228356914</v>
+        <v>162.2232642861696</v>
       </c>
       <c r="E52">
-        <v>16.65000000000001</v>
+        <v>20.035</v>
       </c>
       <c r="F52">
-        <v>169.25</v>
+        <v>172.635</v>
       </c>
       <c r="G52">
         <v>9.84</v>
@@ -5545,28 +5545,28 @@
         <v>21.6</v>
       </c>
       <c r="M52">
-        <v>24.8459</v>
+        <v>25.342818</v>
       </c>
       <c r="N52">
-        <v>-3.245900000000002</v>
+        <v>-3.742818</v>
       </c>
       <c r="O52">
         <v>-0</v>
       </c>
       <c r="P52">
-        <v>-3.245900000000002</v>
+        <v>-3.742818</v>
       </c>
       <c r="Q52">
-        <v>5.154099999999998</v>
+        <v>4.657182000000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1187282433347145</v>
+        <v>0.1202165748313413</v>
       </c>
       <c r="T52">
-        <v>1.421507203861522</v>
+        <v>1.450517554960736</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8693587271944263</v>
+        <v>0.8523124776415946</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1337741216673572</v>
+        <v>0.1347841216673572</v>
       </c>
       <c r="C53">
-        <v>-0.5717357138303498</v>
+        <v>-5.798024854622497</v>
       </c>
       <c r="D53">
-        <v>162.2232642861696</v>
+        <v>160.3819751453775</v>
       </c>
       <c r="E53">
-        <v>20.035</v>
+        <v>23.42000000000002</v>
       </c>
       <c r="F53">
-        <v>172.635</v>
+        <v>176.02</v>
       </c>
       <c r="G53">
         <v>9.84</v>
@@ -5627,28 +5627,28 @@
         <v>21.6</v>
       </c>
       <c r="M53">
-        <v>25.342818</v>
+        <v>25.83973600000001</v>
       </c>
       <c r="N53">
-        <v>-3.742818</v>
+        <v>-4.239736000000004</v>
       </c>
       <c r="O53">
         <v>-0</v>
       </c>
       <c r="P53">
-        <v>-3.742818</v>
+        <v>-4.239736000000004</v>
       </c>
       <c r="Q53">
-        <v>4.657182000000001</v>
+        <v>4.160263999999996</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1202165748313413</v>
+        <v>0.1217669201403276</v>
       </c>
       <c r="T53">
-        <v>1.450517554960736</v>
+        <v>1.480736670689085</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8523124776415946</v>
+        <v>0.8359218530715637</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1347841216673572</v>
+        <v>0.1357941216673572</v>
       </c>
       <c r="C54">
-        <v>-5.798024854622497</v>
+        <v>-10.98298458416542</v>
       </c>
       <c r="D54">
-        <v>160.3819751453775</v>
+        <v>158.5820154158346</v>
       </c>
       <c r="E54">
-        <v>23.42000000000002</v>
+        <v>26.80500000000001</v>
       </c>
       <c r="F54">
-        <v>176.02</v>
+        <v>179.405</v>
       </c>
       <c r="G54">
         <v>9.84</v>
@@ -5709,28 +5709,28 @@
         <v>21.6</v>
       </c>
       <c r="M54">
-        <v>25.83973600000001</v>
+        <v>26.336654</v>
       </c>
       <c r="N54">
-        <v>-4.239736000000004</v>
+        <v>-4.736654000000001</v>
       </c>
       <c r="O54">
         <v>-0</v>
       </c>
       <c r="P54">
-        <v>-4.239736000000004</v>
+        <v>-4.736654000000001</v>
       </c>
       <c r="Q54">
-        <v>4.160263999999996</v>
+        <v>3.663345999999999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1217669201403276</v>
+        <v>0.1233832375901218</v>
       </c>
       <c r="T54">
-        <v>1.480736670689085</v>
+        <v>1.512241706235661</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8359218530715637</v>
+        <v>0.8201497426362513</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1357941216673572</v>
+        <v>0.1368041216673572</v>
       </c>
       <c r="C55">
-        <v>-10.98298458416542</v>
+        <v>-16.12799097327652</v>
       </c>
       <c r="D55">
-        <v>158.5820154158346</v>
+        <v>156.8220090267235</v>
       </c>
       <c r="E55">
-        <v>26.80500000000001</v>
+        <v>30.19000000000003</v>
       </c>
       <c r="F55">
-        <v>179.405</v>
+        <v>182.79</v>
       </c>
       <c r="G55">
         <v>9.84</v>
@@ -5791,28 +5791,28 @@
         <v>21.6</v>
       </c>
       <c r="M55">
-        <v>26.336654</v>
+        <v>26.833572</v>
       </c>
       <c r="N55">
-        <v>-4.736654000000001</v>
+        <v>-5.233572000000002</v>
       </c>
       <c r="O55">
         <v>-0</v>
       </c>
       <c r="P55">
-        <v>-4.736654000000001</v>
+        <v>-5.233572000000002</v>
       </c>
       <c r="Q55">
-        <v>3.663345999999999</v>
+        <v>3.166427999999998</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1233832375901218</v>
+        <v>0.1250698297116462</v>
       </c>
       <c r="T55">
-        <v>1.512241706235661</v>
+        <v>1.545116525936436</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8201497426362513</v>
+        <v>0.8049617844392837</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1368041216673572</v>
+        <v>0.1675141216673572</v>
       </c>
       <c r="C56">
-        <v>-16.12799097327652</v>
+        <v>-59.08115144008532</v>
       </c>
       <c r="D56">
-        <v>156.8220090267235</v>
+        <v>117.2538485599147</v>
       </c>
       <c r="E56">
-        <v>30.19000000000003</v>
+        <v>33.57500000000002</v>
       </c>
       <c r="F56">
-        <v>182.79</v>
+        <v>186.175</v>
       </c>
       <c r="G56">
         <v>9.84</v>
@@ -5873,45 +5873,45 @@
         <v>21.6</v>
       </c>
       <c r="M56">
-        <v>26.833572</v>
+        <v>37.38394</v>
       </c>
       <c r="N56">
-        <v>-5.233572000000002</v>
+        <v>-15.78394</v>
       </c>
       <c r="O56">
         <v>-0</v>
       </c>
       <c r="P56">
-        <v>-5.233572000000002</v>
+        <v>-15.78394</v>
       </c>
       <c r="Q56">
-        <v>3.166427999999998</v>
+        <v>-7.383940000000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1250698297116462</v>
+        <v>0.1268313814830161</v>
       </c>
       <c r="T56">
-        <v>1.545116525936436</v>
+        <v>1.579452448735024</v>
       </c>
       <c r="U56">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V56">
         <v>0</v>
       </c>
       <c r="W56">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y56">
-        <v>0.8049617844392837</v>
+        <v>0.5777882160093345</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1675141216673572</v>
+        <v>0.1690641216673572</v>
       </c>
       <c r="C57">
-        <v>-59.08115144008532</v>
+        <v>-63.94057451477632</v>
       </c>
       <c r="D57">
-        <v>117.2538485599147</v>
+        <v>115.7794254852237</v>
       </c>
       <c r="E57">
-        <v>33.57500000000002</v>
+        <v>36.96000000000004</v>
       </c>
       <c r="F57">
-        <v>186.175</v>
+        <v>189.56</v>
       </c>
       <c r="G57">
         <v>9.84</v>
@@ -5955,28 +5955,28 @@
         <v>21.6</v>
       </c>
       <c r="M57">
-        <v>37.38394</v>
+        <v>38.06364800000001</v>
       </c>
       <c r="N57">
-        <v>-15.78394</v>
+        <v>-16.46364800000001</v>
       </c>
       <c r="O57">
         <v>-0</v>
       </c>
       <c r="P57">
-        <v>-15.78394</v>
+        <v>-16.46364800000001</v>
       </c>
       <c r="Q57">
-        <v>-7.383940000000001</v>
+        <v>-8.063648000000006</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1268313814830161</v>
+        <v>0.1286730037894482</v>
       </c>
       <c r="T57">
-        <v>1.579452448735024</v>
+        <v>1.615349095297184</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.5777882160093345</v>
+        <v>0.567470569294882</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1690641216673572</v>
+        <v>0.1706141216673572</v>
       </c>
       <c r="C58">
-        <v>-63.94057451477632</v>
+        <v>-68.76337744207943</v>
       </c>
       <c r="D58">
-        <v>115.7794254852237</v>
+        <v>114.3416225579206</v>
       </c>
       <c r="E58">
-        <v>36.96000000000004</v>
+        <v>40.34500000000003</v>
       </c>
       <c r="F58">
-        <v>189.56</v>
+        <v>192.945</v>
       </c>
       <c r="G58">
         <v>9.84</v>
@@ -6037,28 +6037,28 @@
         <v>21.6</v>
       </c>
       <c r="M58">
-        <v>38.06364800000001</v>
+        <v>38.74335600000001</v>
       </c>
       <c r="N58">
-        <v>-16.46364800000001</v>
+        <v>-17.143356</v>
       </c>
       <c r="O58">
         <v>-0</v>
       </c>
       <c r="P58">
-        <v>-16.46364800000001</v>
+        <v>-17.143356</v>
       </c>
       <c r="Q58">
-        <v>-8.063648000000006</v>
+        <v>-8.743356000000004</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1286730037894482</v>
+        <v>0.1306002829473424</v>
       </c>
       <c r="T58">
-        <v>1.615349095297184</v>
+        <v>1.652915353327351</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.567470569294882</v>
+        <v>0.5575149452721648</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1706141216673572</v>
+        <v>0.1721641216673572</v>
       </c>
       <c r="C59">
-        <v>-68.76337744207943</v>
+        <v>-73.55090778555237</v>
       </c>
       <c r="D59">
-        <v>114.3416225579206</v>
+        <v>112.9390922144476</v>
       </c>
       <c r="E59">
-        <v>40.34500000000003</v>
+        <v>43.73000000000002</v>
       </c>
       <c r="F59">
-        <v>192.945</v>
+        <v>196.33</v>
       </c>
       <c r="G59">
         <v>9.84</v>
@@ -6119,28 +6119,28 @@
         <v>21.6</v>
       </c>
       <c r="M59">
-        <v>38.74335600000001</v>
+        <v>39.423064</v>
       </c>
       <c r="N59">
-        <v>-17.143356</v>
+        <v>-17.823064</v>
       </c>
       <c r="O59">
         <v>-0</v>
       </c>
       <c r="P59">
-        <v>-17.143356</v>
+        <v>-17.823064</v>
       </c>
       <c r="Q59">
-        <v>-8.743356000000004</v>
+        <v>-9.423064000000002</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1306002829473424</v>
+        <v>0.1326193373032315</v>
       </c>
       <c r="T59">
-        <v>1.652915353327351</v>
+        <v>1.692270480787526</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5575149452721648</v>
+        <v>0.5479026186295413</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1721641216673572</v>
+        <v>0.1737141216673572</v>
       </c>
       <c r="C60">
-        <v>-73.55090778555234</v>
+        <v>-78.30444779232056</v>
       </c>
       <c r="D60">
-        <v>112.9390922144476</v>
+        <v>111.5705522076794</v>
       </c>
       <c r="E60">
-        <v>43.72999999999999</v>
+        <v>47.11500000000001</v>
       </c>
       <c r="F60">
-        <v>196.33</v>
+        <v>199.715</v>
       </c>
       <c r="G60">
         <v>9.84</v>
@@ -6201,28 +6201,28 @@
         <v>21.6</v>
       </c>
       <c r="M60">
-        <v>39.423064</v>
+        <v>40.102772</v>
       </c>
       <c r="N60">
-        <v>-17.823064</v>
+        <v>-18.502772</v>
       </c>
       <c r="O60">
         <v>-0</v>
       </c>
       <c r="P60">
-        <v>-17.823064</v>
+        <v>-18.502772</v>
       </c>
       <c r="Q60">
-        <v>-9.423063999999995</v>
+        <v>-10.102772</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1326193373032315</v>
+        <v>0.1347368821155054</v>
       </c>
       <c r="T60">
-        <v>1.692270480787525</v>
+        <v>1.733545370562831</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5479026186295415</v>
+        <v>0.5386161335680237</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1737141216673572</v>
+        <v>0.1752641216673572</v>
       </c>
       <c r="C61">
-        <v>-78.30444779232056</v>
+        <v>-83.02521830305898</v>
       </c>
       <c r="D61">
-        <v>111.5705522076794</v>
+        <v>110.234781696941</v>
       </c>
       <c r="E61">
-        <v>47.11500000000001</v>
+        <v>50.5</v>
       </c>
       <c r="F61">
-        <v>199.715</v>
+        <v>203.1</v>
       </c>
       <c r="G61">
         <v>9.84</v>
@@ -6283,28 +6283,28 @@
         <v>21.6</v>
       </c>
       <c r="M61">
-        <v>40.102772</v>
+        <v>40.78248</v>
       </c>
       <c r="N61">
-        <v>-18.502772</v>
+        <v>-19.18248</v>
       </c>
       <c r="O61">
         <v>-0</v>
       </c>
       <c r="P61">
-        <v>-18.502772</v>
+        <v>-19.18248</v>
       </c>
       <c r="Q61">
-        <v>-10.102772</v>
+        <v>-10.78248</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1347368821155054</v>
+        <v>0.1369603041683931</v>
       </c>
       <c r="T61">
-        <v>1.733545370562831</v>
+        <v>1.776884004826902</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5386161335680237</v>
+        <v>0.5296391980085566</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1752641216673572</v>
+        <v>0.1768141216673572</v>
       </c>
       <c r="C62">
-        <v>-83.02521830305898</v>
+        <v>-87.71438238442475</v>
       </c>
       <c r="D62">
-        <v>110.234781696941</v>
+        <v>108.9306176155752</v>
       </c>
       <c r="E62">
-        <v>50.5</v>
+        <v>53.88499999999999</v>
       </c>
       <c r="F62">
-        <v>203.1</v>
+        <v>206.485</v>
       </c>
       <c r="G62">
         <v>9.84</v>
@@ -6365,28 +6365,28 @@
         <v>21.6</v>
       </c>
       <c r="M62">
-        <v>40.78248</v>
+        <v>41.462188</v>
       </c>
       <c r="N62">
-        <v>-19.18248</v>
+        <v>-19.862188</v>
       </c>
       <c r="O62">
         <v>-0</v>
       </c>
       <c r="P62">
-        <v>-19.18248</v>
+        <v>-19.862188</v>
       </c>
       <c r="Q62">
-        <v>-10.78248</v>
+        <v>-11.462188</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1369603041683931</v>
+        <v>0.1392977478650185</v>
       </c>
       <c r="T62">
-        <v>1.776884004826902</v>
+        <v>1.822445133155797</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5296391980085566</v>
+        <v>0.5209565882051377</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1768141216673572</v>
+        <v>0.1783641216673572</v>
       </c>
       <c r="C63">
-        <v>-87.71438238442475</v>
+        <v>-92.37304870665801</v>
       </c>
       <c r="D63">
-        <v>108.9306176155752</v>
+        <v>107.656951293342</v>
       </c>
       <c r="E63">
-        <v>53.88499999999999</v>
+        <v>57.27000000000001</v>
       </c>
       <c r="F63">
-        <v>206.485</v>
+        <v>209.87</v>
       </c>
       <c r="G63">
         <v>9.84</v>
@@ -6447,28 +6447,28 @@
         <v>21.6</v>
       </c>
       <c r="M63">
-        <v>41.462188</v>
+        <v>42.141896</v>
       </c>
       <c r="N63">
-        <v>-19.862188</v>
+        <v>-20.541896</v>
       </c>
       <c r="O63">
         <v>-0</v>
       </c>
       <c r="P63">
-        <v>-19.862188</v>
+        <v>-20.541896</v>
       </c>
       <c r="Q63">
-        <v>-11.462188</v>
+        <v>-12.141896</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1392977478650185</v>
+        <v>0.141758214914098</v>
       </c>
       <c r="T63">
-        <v>1.822445133155797</v>
+        <v>1.870404215607265</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5209565882051377</v>
+        <v>0.5125540625889258</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1783641216673572</v>
+        <v>0.1799141216673572</v>
       </c>
       <c r="C64">
-        <v>-92.37304870665801</v>
+        <v>-97.00227468696576</v>
       </c>
       <c r="D64">
-        <v>107.656951293342</v>
+        <v>106.4127253130342</v>
       </c>
       <c r="E64">
-        <v>57.27000000000001</v>
+        <v>60.655</v>
       </c>
       <c r="F64">
-        <v>209.87</v>
+        <v>213.255</v>
       </c>
       <c r="G64">
         <v>9.84</v>
@@ -6529,28 +6529,28 @@
         <v>21.6</v>
       </c>
       <c r="M64">
-        <v>42.141896</v>
+        <v>42.821604</v>
       </c>
       <c r="N64">
-        <v>-20.541896</v>
+        <v>-21.221604</v>
       </c>
       <c r="O64">
         <v>-0</v>
       </c>
       <c r="P64">
-        <v>-20.541896</v>
+        <v>-21.221604</v>
       </c>
       <c r="Q64">
-        <v>-12.141896</v>
+        <v>-12.821604</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.141758214914098</v>
+        <v>0.1443516801820466</v>
       </c>
       <c r="T64">
-        <v>1.870404215607265</v>
+        <v>1.920955680893948</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5125540625889258</v>
+        <v>0.504418283817673</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1799141216673572</v>
+        <v>0.2038641216673572</v>
       </c>
       <c r="C65">
-        <v>-97.00227468696576</v>
+        <v>-116.5110144981458</v>
       </c>
       <c r="D65">
-        <v>106.4127253130342</v>
+        <v>90.28898550185423</v>
       </c>
       <c r="E65">
-        <v>60.655</v>
+        <v>64.04000000000002</v>
       </c>
       <c r="F65">
-        <v>213.255</v>
+        <v>216.64</v>
       </c>
       <c r="G65">
         <v>9.84</v>
@@ -6611,45 +6611,45 @@
         <v>21.6</v>
       </c>
       <c r="M65">
-        <v>42.821604</v>
+        <v>51.08371200000001</v>
       </c>
       <c r="N65">
-        <v>-21.221604</v>
+        <v>-29.483712</v>
       </c>
       <c r="O65">
         <v>-0</v>
       </c>
       <c r="P65">
-        <v>-21.221604</v>
+        <v>-29.483712</v>
       </c>
       <c r="Q65">
-        <v>-12.821604</v>
+        <v>-21.08371200000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1443516801820466</v>
+        <v>0.1470892268537701</v>
       </c>
       <c r="T65">
-        <v>1.920955680893948</v>
+        <v>1.97431556091878</v>
       </c>
       <c r="U65">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V65">
         <v>0</v>
       </c>
       <c r="W65">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.504418283817673</v>
+        <v>0.4228353648223527</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2038641216673572</v>
+        <v>0.2057641216673572</v>
       </c>
       <c r="C66">
-        <v>-116.5110144981458</v>
+        <v>-120.968436680479</v>
       </c>
       <c r="D66">
-        <v>90.28898550185423</v>
+        <v>89.216563319521</v>
       </c>
       <c r="E66">
-        <v>64.04000000000002</v>
+        <v>67.42500000000001</v>
       </c>
       <c r="F66">
-        <v>216.64</v>
+        <v>220.025</v>
       </c>
       <c r="G66">
         <v>9.84</v>
@@ -6693,28 +6693,28 @@
         <v>21.6</v>
       </c>
       <c r="M66">
-        <v>51.08371200000001</v>
+        <v>51.881895</v>
       </c>
       <c r="N66">
-        <v>-29.483712</v>
+        <v>-30.281895</v>
       </c>
       <c r="O66">
         <v>-0</v>
       </c>
       <c r="P66">
-        <v>-29.483712</v>
+        <v>-30.281895</v>
       </c>
       <c r="Q66">
-        <v>-21.08371200000001</v>
+        <v>-21.881895</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1470892268537701</v>
+        <v>0.1499832047638778</v>
       </c>
       <c r="T66">
-        <v>1.97431556091878</v>
+        <v>2.030724576945031</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.4228353648223527</v>
+        <v>0.4163302053635474</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2057641216673572</v>
+        <v>0.2076641216673572</v>
       </c>
       <c r="C67">
-        <v>-120.968436680479</v>
+        <v>-125.4006821636717</v>
       </c>
       <c r="D67">
-        <v>89.216563319521</v>
+        <v>88.16931783632833</v>
       </c>
       <c r="E67">
-        <v>67.42500000000001</v>
+        <v>70.81</v>
       </c>
       <c r="F67">
-        <v>220.025</v>
+        <v>223.41</v>
       </c>
       <c r="G67">
         <v>9.84</v>
@@ -6775,28 +6775,28 @@
         <v>21.6</v>
       </c>
       <c r="M67">
-        <v>51.881895</v>
+        <v>52.680078</v>
       </c>
       <c r="N67">
-        <v>-30.281895</v>
+        <v>-31.080078</v>
       </c>
       <c r="O67">
         <v>-0</v>
       </c>
       <c r="P67">
-        <v>-30.281895</v>
+        <v>-31.080078</v>
       </c>
       <c r="Q67">
-        <v>-21.881895</v>
+        <v>-22.680078</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1499832047638778</v>
+        <v>0.1530474166686977</v>
       </c>
       <c r="T67">
-        <v>2.030724576945031</v>
+        <v>2.090451770384591</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.4163302053635474</v>
+        <v>0.4100221719489482</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2076641216673572</v>
+        <v>0.2095641216673572</v>
       </c>
       <c r="C68">
-        <v>-125.4006821636717</v>
+        <v>-129.8086272519084</v>
       </c>
       <c r="D68">
-        <v>88.16931783632833</v>
+        <v>87.14637274809159</v>
       </c>
       <c r="E68">
-        <v>70.81</v>
+        <v>74.19500000000002</v>
       </c>
       <c r="F68">
-        <v>223.41</v>
+        <v>226.795</v>
       </c>
       <c r="G68">
         <v>9.84</v>
@@ -6857,28 +6857,28 @@
         <v>21.6</v>
       </c>
       <c r="M68">
-        <v>52.680078</v>
+        <v>53.478261</v>
       </c>
       <c r="N68">
-        <v>-31.080078</v>
+        <v>-31.878261</v>
       </c>
       <c r="O68">
         <v>-0</v>
       </c>
       <c r="P68">
-        <v>-31.080078</v>
+        <v>-31.878261</v>
       </c>
       <c r="Q68">
-        <v>-22.680078</v>
+        <v>-23.478261</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1530474166686977</v>
+        <v>0.156297338385931</v>
       </c>
       <c r="T68">
-        <v>2.090451770384591</v>
+        <v>2.153798793729578</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4100221719489482</v>
+        <v>0.4039024380392624</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2095641216673572</v>
+        <v>0.2114641216673572</v>
       </c>
       <c r="C69">
-        <v>-129.8086272519084</v>
+        <v>-134.1931080480813</v>
       </c>
       <c r="D69">
-        <v>87.14637274809159</v>
+        <v>86.1468919519187</v>
       </c>
       <c r="E69">
-        <v>74.19500000000002</v>
+        <v>77.58000000000001</v>
       </c>
       <c r="F69">
-        <v>226.795</v>
+        <v>230.18</v>
       </c>
       <c r="G69">
         <v>9.84</v>
@@ -6939,28 +6939,28 @@
         <v>21.6</v>
       </c>
       <c r="M69">
-        <v>53.478261</v>
+        <v>54.27644400000001</v>
       </c>
       <c r="N69">
-        <v>-31.878261</v>
+        <v>-32.676444</v>
       </c>
       <c r="O69">
         <v>-0</v>
       </c>
       <c r="P69">
-        <v>-31.878261</v>
+        <v>-32.676444</v>
       </c>
       <c r="Q69">
-        <v>-23.478261</v>
+        <v>-24.27644400000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.156297338385931</v>
+        <v>0.1597503802104913</v>
       </c>
       <c r="T69">
-        <v>2.153798793729578</v>
+        <v>2.221105006033627</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.4039024380392624</v>
+        <v>0.3979626963033909</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2114641216673572</v>
+        <v>0.2133641216673572</v>
       </c>
       <c r="C70">
-        <v>-134.1931080480813</v>
+        <v>-138.5549227329909</v>
       </c>
       <c r="D70">
-        <v>86.1468919519187</v>
+        <v>85.17007726700916</v>
       </c>
       <c r="E70">
-        <v>77.58000000000001</v>
+        <v>80.96500000000003</v>
       </c>
       <c r="F70">
-        <v>230.18</v>
+        <v>233.565</v>
       </c>
       <c r="G70">
         <v>9.84</v>
@@ -7021,28 +7021,28 @@
         <v>21.6</v>
       </c>
       <c r="M70">
-        <v>54.27644400000001</v>
+        <v>55.07462700000001</v>
       </c>
       <c r="N70">
-        <v>-32.676444</v>
+        <v>-33.47462700000001</v>
       </c>
       <c r="O70">
         <v>-0</v>
       </c>
       <c r="P70">
-        <v>-32.676444</v>
+        <v>-33.47462700000001</v>
       </c>
       <c r="Q70">
-        <v>-24.27644400000001</v>
+        <v>-25.07462700000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1597503802104913</v>
+        <v>0.1634261989269588</v>
       </c>
       <c r="T70">
-        <v>2.221105006033627</v>
+        <v>2.292753554615358</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3979626963033909</v>
+        <v>0.392195120994646</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2133641216673572</v>
+        <v>0.2152641216673572</v>
       </c>
       <c r="C71">
-        <v>-138.5549227329909</v>
+        <v>-142.8948336912229</v>
       </c>
       <c r="D71">
-        <v>85.17007726700916</v>
+        <v>84.21516630877714</v>
       </c>
       <c r="E71">
-        <v>80.96500000000003</v>
+        <v>84.35000000000002</v>
       </c>
       <c r="F71">
-        <v>233.565</v>
+        <v>236.95</v>
       </c>
       <c r="G71">
         <v>9.84</v>
@@ -7103,28 +7103,28 @@
         <v>21.6</v>
       </c>
       <c r="M71">
-        <v>55.07462700000001</v>
+        <v>55.87281000000001</v>
       </c>
       <c r="N71">
-        <v>-33.47462700000001</v>
+        <v>-34.27281000000001</v>
       </c>
       <c r="O71">
         <v>-0</v>
       </c>
       <c r="P71">
-        <v>-33.47462700000001</v>
+        <v>-34.27281000000001</v>
       </c>
       <c r="Q71">
-        <v>-25.07462700000001</v>
+        <v>-25.87281000000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1634261989269588</v>
+        <v>0.1673470722245241</v>
       </c>
       <c r="T71">
-        <v>2.292753554615358</v>
+        <v>2.369178673102536</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.392195120994646</v>
+        <v>0.3865923335518654</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2152641216673572</v>
+        <v>0.2171641216673572</v>
       </c>
       <c r="C72">
-        <v>-142.8948336912229</v>
+        <v>-147.2135694956013</v>
       </c>
       <c r="D72">
-        <v>84.21516630877714</v>
+        <v>83.2814305043987</v>
       </c>
       <c r="E72">
-        <v>84.35000000000002</v>
+        <v>87.73500000000004</v>
       </c>
       <c r="F72">
-        <v>236.95</v>
+        <v>240.335</v>
       </c>
       <c r="G72">
         <v>9.84</v>
@@ -7185,28 +7185,28 @@
         <v>21.6</v>
       </c>
       <c r="M72">
-        <v>55.87281000000001</v>
+        <v>56.67099300000001</v>
       </c>
       <c r="N72">
-        <v>-34.27281000000001</v>
+        <v>-35.07099300000001</v>
       </c>
       <c r="O72">
         <v>-0</v>
       </c>
       <c r="P72">
-        <v>-34.27281000000001</v>
+        <v>-35.07099300000001</v>
       </c>
       <c r="Q72">
-        <v>-25.87281000000001</v>
+        <v>-26.67099300000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1673470722245241</v>
+        <v>0.1715383505770939</v>
       </c>
       <c r="T72">
-        <v>2.369178673102536</v>
+        <v>2.450874489416417</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3865923335518654</v>
+        <v>0.3811473711074729</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2171641216673572</v>
+        <v>0.2190641216673572</v>
       </c>
       <c r="C73">
-        <v>-147.2135694956013</v>
+        <v>-151.5118267610733</v>
       </c>
       <c r="D73">
-        <v>83.2814305043987</v>
+        <v>82.36817323892664</v>
       </c>
       <c r="E73">
-        <v>87.73499999999999</v>
+        <v>91.12</v>
       </c>
       <c r="F73">
-        <v>240.335</v>
+        <v>243.72</v>
       </c>
       <c r="G73">
         <v>9.84</v>
@@ -7267,28 +7267,28 @@
         <v>21.6</v>
       </c>
       <c r="M73">
-        <v>56.670993</v>
+        <v>57.469176</v>
       </c>
       <c r="N73">
-        <v>-35.07099299999999</v>
+        <v>-35.869176</v>
       </c>
       <c r="O73">
         <v>-0</v>
       </c>
       <c r="P73">
-        <v>-35.07099299999999</v>
+        <v>-35.869176</v>
       </c>
       <c r="Q73">
-        <v>-26.670993</v>
+        <v>-27.469176</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1715383505770939</v>
+        <v>0.1760290059548472</v>
       </c>
       <c r="T73">
-        <v>2.450874489416416</v>
+        <v>2.538405721181288</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.381147371107473</v>
+        <v>0.3758536576198691</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2190641216673572</v>
+        <v>0.2209641216673572</v>
       </c>
       <c r="C74">
-        <v>-151.5118267610733</v>
+        <v>-155.7902718779401</v>
       </c>
       <c r="D74">
-        <v>82.36817323892664</v>
+        <v>81.47472812205986</v>
       </c>
       <c r="E74">
-        <v>91.12</v>
+        <v>94.505</v>
       </c>
       <c r="F74">
-        <v>243.72</v>
+        <v>247.105</v>
       </c>
       <c r="G74">
         <v>9.84</v>
@@ -7349,28 +7349,28 @@
         <v>21.6</v>
       </c>
       <c r="M74">
-        <v>57.469176</v>
+        <v>58.267359</v>
       </c>
       <c r="N74">
-        <v>-35.869176</v>
+        <v>-36.667359</v>
       </c>
       <c r="O74">
         <v>-0</v>
       </c>
       <c r="P74">
-        <v>-35.869176</v>
+        <v>-36.667359</v>
       </c>
       <c r="Q74">
-        <v>-27.469176</v>
+        <v>-28.267359</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1760290059548472</v>
+        <v>0.1808523024716934</v>
       </c>
       <c r="T74">
-        <v>2.538405721181288</v>
+        <v>2.632420747891706</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3758536576198691</v>
+        <v>0.3707049773785011</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2209641216673572</v>
+        <v>0.2228641216673573</v>
       </c>
       <c r="C75">
-        <v>-155.7902718779401</v>
+        <v>-160.0495426334958</v>
       </c>
       <c r="D75">
-        <v>81.47472812205986</v>
+        <v>80.60045736650423</v>
       </c>
       <c r="E75">
-        <v>94.505</v>
+        <v>97.89000000000001</v>
       </c>
       <c r="F75">
-        <v>247.105</v>
+        <v>250.49</v>
       </c>
       <c r="G75">
         <v>9.84</v>
@@ -7431,28 +7431,28 @@
         <v>21.6</v>
       </c>
       <c r="M75">
-        <v>58.267359</v>
+        <v>59.06554200000001</v>
       </c>
       <c r="N75">
-        <v>-36.667359</v>
+        <v>-37.46554200000001</v>
       </c>
       <c r="O75">
         <v>-0</v>
       </c>
       <c r="P75">
-        <v>-36.667359</v>
+        <v>-37.46554200000001</v>
       </c>
       <c r="Q75">
-        <v>-28.267359</v>
+        <v>-29.06554200000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1808523024716934</v>
+        <v>0.1860466217975278</v>
       </c>
       <c r="T75">
-        <v>2.632420747891706</v>
+        <v>2.733667699733695</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3707049773785011</v>
+        <v>0.3656954506571699</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2228641216673573</v>
+        <v>0.2247641216673572</v>
       </c>
       <c r="C76">
-        <v>-160.0495426334958</v>
+        <v>-164.2902497303686</v>
       </c>
       <c r="D76">
-        <v>80.60045736650423</v>
+        <v>79.74475026963138</v>
       </c>
       <c r="E76">
-        <v>97.89000000000001</v>
+        <v>101.275</v>
       </c>
       <c r="F76">
-        <v>250.49</v>
+        <v>253.875</v>
       </c>
       <c r="G76">
         <v>9.84</v>
@@ -7513,28 +7513,28 @@
         <v>21.6</v>
       </c>
       <c r="M76">
-        <v>59.06554200000001</v>
+        <v>59.863725</v>
       </c>
       <c r="N76">
-        <v>-37.46554200000001</v>
+        <v>-38.263725</v>
       </c>
       <c r="O76">
         <v>-0</v>
       </c>
       <c r="P76">
-        <v>-37.46554200000001</v>
+        <v>-38.263725</v>
       </c>
       <c r="Q76">
-        <v>-29.06554200000001</v>
+        <v>-29.863725</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1860466217975278</v>
+        <v>0.1916564866694289</v>
       </c>
       <c r="T76">
-        <v>2.733667699733695</v>
+        <v>2.843014407723043</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3656954506571699</v>
+        <v>0.3608195113150744</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2247641216673572</v>
+        <v>0.2266641216673572</v>
       </c>
       <c r="C77">
-        <v>-164.2902497303686</v>
+        <v>-168.5129782091597</v>
       </c>
       <c r="D77">
-        <v>79.74475026963138</v>
+        <v>78.90702179084028</v>
       </c>
       <c r="E77">
-        <v>101.275</v>
+        <v>104.66</v>
       </c>
       <c r="F77">
-        <v>253.875</v>
+        <v>257.26</v>
       </c>
       <c r="G77">
         <v>9.84</v>
@@ -7595,28 +7595,28 @@
         <v>21.6</v>
       </c>
       <c r="M77">
-        <v>59.863725</v>
+        <v>60.661908</v>
       </c>
       <c r="N77">
-        <v>-38.263725</v>
+        <v>-39.061908</v>
       </c>
       <c r="O77">
         <v>-0</v>
       </c>
       <c r="P77">
-        <v>-38.263725</v>
+        <v>-39.061908</v>
       </c>
       <c r="Q77">
-        <v>-29.863725</v>
+        <v>-30.661908</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1916564866694289</v>
+        <v>0.1977338402806551</v>
       </c>
       <c r="T77">
-        <v>2.843014407723043</v>
+        <v>2.96147334137817</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3608195113150744</v>
+        <v>0.3560718861661919</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2266641216673572</v>
+        <v>0.2285641216673572</v>
       </c>
       <c r="C78">
-        <v>-168.5129782091597</v>
+        <v>-172.7182887823447</v>
       </c>
       <c r="D78">
-        <v>78.90702179084028</v>
+        <v>78.08671121765528</v>
       </c>
       <c r="E78">
-        <v>104.66</v>
+        <v>108.045</v>
       </c>
       <c r="F78">
-        <v>257.26</v>
+        <v>260.645</v>
       </c>
       <c r="G78">
         <v>9.84</v>
@@ -7677,28 +7677,28 @@
         <v>21.6</v>
       </c>
       <c r="M78">
-        <v>60.661908</v>
+        <v>61.460091</v>
       </c>
       <c r="N78">
-        <v>-39.061908</v>
+        <v>-39.860091</v>
       </c>
       <c r="O78">
         <v>-0</v>
       </c>
       <c r="P78">
-        <v>-39.061908</v>
+        <v>-39.860091</v>
       </c>
       <c r="Q78">
-        <v>-30.661908</v>
+        <v>-31.460091</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1977338402806551</v>
+        <v>0.2043396594232923</v>
       </c>
       <c r="T78">
-        <v>2.96147334137817</v>
+        <v>3.090233051872873</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3560718861661919</v>
+        <v>0.3514475759562413</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2285641216673572</v>
+        <v>0.2304641216673572</v>
       </c>
       <c r="C79">
-        <v>-172.7182887823447</v>
+        <v>-176.9067190858273</v>
       </c>
       <c r="D79">
-        <v>78.08671121765528</v>
+        <v>77.28328091417271</v>
       </c>
       <c r="E79">
-        <v>108.045</v>
+        <v>111.43</v>
       </c>
       <c r="F79">
-        <v>260.645</v>
+        <v>264.03</v>
       </c>
       <c r="G79">
         <v>9.84</v>
@@ -7759,28 +7759,28 @@
         <v>21.6</v>
       </c>
       <c r="M79">
-        <v>61.460091</v>
+        <v>62.25827400000001</v>
       </c>
       <c r="N79">
-        <v>-39.860091</v>
+        <v>-40.65827400000001</v>
       </c>
       <c r="O79">
         <v>-0</v>
       </c>
       <c r="P79">
-        <v>-39.860091</v>
+        <v>-40.65827400000001</v>
       </c>
       <c r="Q79">
-        <v>-31.460091</v>
+        <v>-32.25827400000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2043396594232923</v>
+        <v>0.2115460075788965</v>
       </c>
       <c r="T79">
-        <v>3.090233051872873</v>
+        <v>3.230698190594367</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3514475759562413</v>
+        <v>0.3469418378029561</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2304641216673572</v>
+        <v>0.2323641216673572</v>
       </c>
       <c r="C80">
-        <v>-176.9067190858273</v>
+        <v>-181.078784854018</v>
       </c>
       <c r="D80">
-        <v>77.28328091417271</v>
+        <v>76.49621514598206</v>
       </c>
       <c r="E80">
-        <v>111.43</v>
+        <v>114.815</v>
       </c>
       <c r="F80">
-        <v>264.03</v>
+        <v>267.415</v>
       </c>
       <c r="G80">
         <v>9.84</v>
@@ -7841,28 +7841,28 @@
         <v>21.6</v>
       </c>
       <c r="M80">
-        <v>62.25827400000001</v>
+        <v>63.05645700000001</v>
       </c>
       <c r="N80">
-        <v>-40.65827400000001</v>
+        <v>-41.45645700000001</v>
       </c>
       <c r="O80">
         <v>-0</v>
       </c>
       <c r="P80">
-        <v>-40.65827400000001</v>
+        <v>-41.45645700000001</v>
       </c>
       <c r="Q80">
-        <v>-32.25827400000001</v>
+        <v>-33.05645700000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2115460075788965</v>
+        <v>0.219438674606463</v>
       </c>
       <c r="T80">
-        <v>3.230698190594367</v>
+        <v>3.384540961575052</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3469418378029561</v>
+        <v>0.3425501689700072</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2323641216673572</v>
+        <v>0.2342641216673572</v>
       </c>
       <c r="C81">
-        <v>-181.078784854018</v>
+        <v>-185.2349810238327</v>
       </c>
       <c r="D81">
-        <v>76.49621514598206</v>
+        <v>75.72501897616733</v>
       </c>
       <c r="E81">
-        <v>114.815</v>
+        <v>118.2</v>
       </c>
       <c r="F81">
-        <v>267.415</v>
+        <v>270.8</v>
       </c>
       <c r="G81">
         <v>9.84</v>
@@ -7923,28 +7923,28 @@
         <v>21.6</v>
       </c>
       <c r="M81">
-        <v>63.05645700000001</v>
+        <v>63.85464</v>
       </c>
       <c r="N81">
-        <v>-41.45645700000001</v>
+        <v>-42.25464</v>
       </c>
       <c r="O81">
         <v>-0</v>
       </c>
       <c r="P81">
-        <v>-41.45645700000001</v>
+        <v>-42.25464</v>
       </c>
       <c r="Q81">
-        <v>-33.05645700000001</v>
+        <v>-33.85464</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.219438674606463</v>
+        <v>0.2281206083367862</v>
       </c>
       <c r="T81">
-        <v>3.384540961575052</v>
+        <v>3.553768009653804</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3425501689700072</v>
+        <v>0.3382682918578822</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2342641216673572</v>
+        <v>0.2361641216673573</v>
       </c>
       <c r="C82">
-        <v>-185.2349810238327</v>
+        <v>-189.3757827725789</v>
       </c>
       <c r="D82">
-        <v>75.72501897616733</v>
+        <v>74.96921722742113</v>
       </c>
       <c r="E82">
-        <v>118.2</v>
+        <v>121.585</v>
       </c>
       <c r="F82">
-        <v>270.8</v>
+        <v>274.185</v>
       </c>
       <c r="G82">
         <v>9.84</v>
@@ -8005,28 +8005,28 @@
         <v>21.6</v>
       </c>
       <c r="M82">
-        <v>63.85464</v>
+        <v>64.652823</v>
       </c>
       <c r="N82">
-        <v>-42.25464</v>
+        <v>-43.052823</v>
       </c>
       <c r="O82">
         <v>-0</v>
       </c>
       <c r="P82">
-        <v>-42.25464</v>
+        <v>-43.052823</v>
       </c>
       <c r="Q82">
-        <v>-33.85464</v>
+        <v>-34.652823</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2281206083367862</v>
+        <v>0.237716429828196</v>
       </c>
       <c r="T82">
-        <v>3.553768009653804</v>
+        <v>3.740808431214531</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3382682918578822</v>
+        <v>0.3340921401065504</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2361641216673573</v>
+        <v>0.2380641216673572</v>
       </c>
       <c r="C83">
-        <v>-189.3757827725789</v>
+        <v>-193.5016464943009</v>
       </c>
       <c r="D83">
-        <v>74.96921722742113</v>
+        <v>74.22835350569913</v>
       </c>
       <c r="E83">
-        <v>121.585</v>
+        <v>124.97</v>
       </c>
       <c r="F83">
-        <v>274.185</v>
+        <v>277.57</v>
       </c>
       <c r="G83">
         <v>9.84</v>
@@ -8087,28 +8087,28 @@
         <v>21.6</v>
       </c>
       <c r="M83">
-        <v>64.652823</v>
+        <v>65.45100600000001</v>
       </c>
       <c r="N83">
-        <v>-43.052823</v>
+        <v>-43.85100600000001</v>
       </c>
       <c r="O83">
         <v>-0</v>
       </c>
       <c r="P83">
-        <v>-43.052823</v>
+        <v>-43.85100600000001</v>
       </c>
       <c r="Q83">
-        <v>-34.652823</v>
+        <v>-35.45100600000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.237716429828196</v>
+        <v>0.2483784537075402</v>
       </c>
       <c r="T83">
-        <v>3.740808431214531</v>
+        <v>3.948631121837561</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3340921401065504</v>
+        <v>0.330017845715007</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2380641216673572</v>
+        <v>0.2399641216673573</v>
       </c>
       <c r="C84">
-        <v>-193.5016464943009</v>
+        <v>-197.6130107188019</v>
       </c>
       <c r="D84">
-        <v>74.22835350569913</v>
+        <v>73.50198928119814</v>
       </c>
       <c r="E84">
-        <v>124.97</v>
+        <v>128.355</v>
       </c>
       <c r="F84">
-        <v>277.57</v>
+        <v>280.955</v>
       </c>
       <c r="G84">
         <v>9.84</v>
@@ -8169,28 +8169,28 @@
         <v>21.6</v>
       </c>
       <c r="M84">
-        <v>65.45100600000001</v>
+        <v>66.24918900000002</v>
       </c>
       <c r="N84">
-        <v>-43.85100600000001</v>
+        <v>-44.64918900000001</v>
       </c>
       <c r="O84">
         <v>-0</v>
       </c>
       <c r="P84">
-        <v>-43.85100600000001</v>
+        <v>-44.64918900000001</v>
       </c>
       <c r="Q84">
-        <v>-35.45100600000001</v>
+        <v>-36.24918900000002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2483784537075402</v>
+        <v>0.2602948333373955</v>
       </c>
       <c r="T84">
-        <v>3.948631121837561</v>
+        <v>4.180903540769182</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.330017845715007</v>
+        <v>0.3260417270919346</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2399641216673573</v>
+        <v>0.2418641216673572</v>
       </c>
       <c r="C85">
-        <v>-197.6130107188019</v>
+        <v>-201.7102969772292</v>
       </c>
       <c r="D85">
-        <v>73.50198928119814</v>
+        <v>72.78970302277079</v>
       </c>
       <c r="E85">
-        <v>128.355</v>
+        <v>131.74</v>
       </c>
       <c r="F85">
-        <v>280.955</v>
+        <v>284.34</v>
       </c>
       <c r="G85">
         <v>9.84</v>
@@ -8251,28 +8251,28 @@
         <v>21.6</v>
       </c>
       <c r="M85">
-        <v>66.24918900000002</v>
+        <v>67.04737200000001</v>
       </c>
       <c r="N85">
-        <v>-44.64918900000001</v>
+        <v>-45.44737200000001</v>
       </c>
       <c r="O85">
         <v>-0</v>
       </c>
       <c r="P85">
-        <v>-44.64918900000001</v>
+        <v>-45.44737200000001</v>
       </c>
       <c r="Q85">
-        <v>-36.24918900000002</v>
+        <v>-37.04737200000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2602948333373955</v>
+        <v>0.2737007604209828</v>
       </c>
       <c r="T85">
-        <v>4.180903540769182</v>
+        <v>4.442210012067258</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3260417270919346</v>
+        <v>0.3221602779598878</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2418641216673572</v>
+        <v>0.2437641216673572</v>
       </c>
       <c r="C86">
-        <v>-201.7102969772291</v>
+        <v>-205.7939106178142</v>
       </c>
       <c r="D86">
-        <v>72.78970302277087</v>
+        <v>72.09108938218576</v>
       </c>
       <c r="E86">
-        <v>131.74</v>
+        <v>135.125</v>
       </c>
       <c r="F86">
-        <v>284.34</v>
+        <v>287.725</v>
       </c>
       <c r="G86">
         <v>9.84</v>
@@ -8333,28 +8333,28 @@
         <v>21.6</v>
       </c>
       <c r="M86">
-        <v>67.047372</v>
+        <v>67.84555499999999</v>
       </c>
       <c r="N86">
-        <v>-45.44737199999999</v>
+        <v>-46.24555499999999</v>
       </c>
       <c r="O86">
         <v>-0</v>
       </c>
       <c r="P86">
-        <v>-45.44737199999999</v>
+        <v>-46.24555499999999</v>
       </c>
       <c r="Q86">
-        <v>-37.047372</v>
+        <v>-37.84555499999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2737007604209826</v>
+        <v>0.2888941444490482</v>
       </c>
       <c r="T86">
-        <v>4.442210012067254</v>
+        <v>4.738357346205071</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3221602779598879</v>
+        <v>0.3183701570427128</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2437641216673572</v>
+        <v>0.2456641216673572</v>
       </c>
       <c r="C87">
-        <v>-205.7939106178142</v>
+        <v>-209.864241575084</v>
       </c>
       <c r="D87">
-        <v>72.09108938218576</v>
+        <v>71.40575842491602</v>
       </c>
       <c r="E87">
-        <v>135.125</v>
+        <v>138.51</v>
       </c>
       <c r="F87">
-        <v>287.725</v>
+        <v>291.11</v>
       </c>
       <c r="G87">
         <v>9.84</v>
@@ -8415,28 +8415,28 @@
         <v>21.6</v>
       </c>
       <c r="M87">
-        <v>67.84555499999999</v>
+        <v>68.643738</v>
       </c>
       <c r="N87">
-        <v>-46.24555499999999</v>
+        <v>-47.043738</v>
       </c>
       <c r="O87">
         <v>-0</v>
       </c>
       <c r="P87">
-        <v>-46.24555499999999</v>
+        <v>-47.043738</v>
       </c>
       <c r="Q87">
-        <v>-37.84555499999999</v>
+        <v>-38.643738</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2888941444490482</v>
+        <v>0.3062580119096944</v>
       </c>
       <c r="T87">
-        <v>4.738357346205071</v>
+        <v>5.076811442362576</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3183701570427128</v>
+        <v>0.3146681784724485</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2456641216673572</v>
+        <v>0.2475641216673572</v>
       </c>
       <c r="C88">
-        <v>-209.864241575084</v>
+        <v>-213.9216650956097</v>
       </c>
       <c r="D88">
-        <v>71.40575842491602</v>
+        <v>70.7333349043903</v>
       </c>
       <c r="E88">
-        <v>138.51</v>
+        <v>141.895</v>
       </c>
       <c r="F88">
-        <v>291.11</v>
+        <v>294.495</v>
       </c>
       <c r="G88">
         <v>9.84</v>
@@ -8497,28 +8497,28 @@
         <v>21.6</v>
       </c>
       <c r="M88">
-        <v>68.643738</v>
+        <v>69.44192100000001</v>
       </c>
       <c r="N88">
-        <v>-47.043738</v>
+        <v>-47.84192100000001</v>
       </c>
       <c r="O88">
         <v>-0</v>
       </c>
       <c r="P88">
-        <v>-47.043738</v>
+        <v>-47.84192100000001</v>
       </c>
       <c r="Q88">
-        <v>-38.643738</v>
+        <v>-39.44192100000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3062580119096944</v>
+        <v>0.3262932435950556</v>
       </c>
       <c r="T88">
-        <v>5.076811442362576</v>
+        <v>5.46733539946739</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3146681784724485</v>
+        <v>0.3110513028578227</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2475641216673572</v>
+        <v>0.2494641216673573</v>
       </c>
       <c r="C89">
-        <v>-213.9216650956097</v>
+        <v>-217.9665424231335</v>
       </c>
       <c r="D89">
-        <v>70.7333349043903</v>
+        <v>70.07345757686652</v>
       </c>
       <c r="E89">
-        <v>141.895</v>
+        <v>145.28</v>
       </c>
       <c r="F89">
-        <v>294.495</v>
+        <v>297.88</v>
       </c>
       <c r="G89">
         <v>9.84</v>
@@ -8579,28 +8579,28 @@
         <v>21.6</v>
       </c>
       <c r="M89">
-        <v>69.44192100000001</v>
+        <v>70.240104</v>
       </c>
       <c r="N89">
-        <v>-47.84192100000001</v>
+        <v>-48.640104</v>
       </c>
       <c r="O89">
         <v>-0</v>
       </c>
       <c r="P89">
-        <v>-47.84192100000001</v>
+        <v>-48.640104</v>
       </c>
       <c r="Q89">
-        <v>-39.44192100000001</v>
+        <v>-40.240104</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3262932435950556</v>
+        <v>0.3496676805613103</v>
       </c>
       <c r="T89">
-        <v>5.46733539946739</v>
+        <v>5.92294668275634</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3110513028578227</v>
+        <v>0.3075166289617112</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2494641216673573</v>
+        <v>0.2513641216673572</v>
       </c>
       <c r="C90">
-        <v>-217.9665424231335</v>
+        <v>-221.9992214456989</v>
       </c>
       <c r="D90">
-        <v>70.07345757686652</v>
+        <v>69.42577855430108</v>
       </c>
       <c r="E90">
-        <v>145.28</v>
+        <v>148.665</v>
       </c>
       <c r="F90">
-        <v>297.88</v>
+        <v>301.265</v>
       </c>
       <c r="G90">
         <v>9.84</v>
@@ -8661,28 +8661,28 @@
         <v>21.6</v>
       </c>
       <c r="M90">
-        <v>70.240104</v>
+        <v>71.038287</v>
       </c>
       <c r="N90">
-        <v>-48.640104</v>
+        <v>-49.438287</v>
       </c>
       <c r="O90">
         <v>-0</v>
       </c>
       <c r="P90">
-        <v>-48.640104</v>
+        <v>-49.438287</v>
       </c>
       <c r="Q90">
-        <v>-40.240104</v>
+        <v>-41.038287</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3496676805613103</v>
+        <v>0.377292015157793</v>
       </c>
       <c r="T90">
-        <v>5.92294668275634</v>
+        <v>6.461396381188734</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3075166289617112</v>
+        <v>0.3040613859396695</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2513641216673572</v>
+        <v>0.2532641216673572</v>
       </c>
       <c r="C91">
-        <v>-221.9992214456989</v>
+        <v>-226.0200373072226</v>
       </c>
       <c r="D91">
-        <v>69.42577855430108</v>
+        <v>68.78996269277744</v>
       </c>
       <c r="E91">
-        <v>148.665</v>
+        <v>152.05</v>
       </c>
       <c r="F91">
-        <v>301.265</v>
+        <v>304.65</v>
       </c>
       <c r="G91">
         <v>9.84</v>
@@ -8743,28 +8743,28 @@
         <v>21.6</v>
       </c>
       <c r="M91">
-        <v>71.038287</v>
+        <v>71.83647000000001</v>
       </c>
       <c r="N91">
-        <v>-49.438287</v>
+        <v>-50.23647</v>
       </c>
       <c r="O91">
         <v>-0</v>
       </c>
       <c r="P91">
-        <v>-49.438287</v>
+        <v>-50.23647</v>
       </c>
       <c r="Q91">
-        <v>-41.038287</v>
+        <v>-41.83647000000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.377292015157793</v>
+        <v>0.4104412166735723</v>
       </c>
       <c r="T91">
-        <v>6.461396381188734</v>
+        <v>7.107536019307608</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3040613859396695</v>
+        <v>0.3006829260958953</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2532641216673572</v>
+        <v>0.2551641216673572</v>
       </c>
       <c r="C92">
-        <v>-226.0200373072226</v>
+        <v>-230.0293129857648</v>
       </c>
       <c r="D92">
-        <v>68.78996269277744</v>
+        <v>68.16568701423525</v>
       </c>
       <c r="E92">
-        <v>152.05</v>
+        <v>155.435</v>
       </c>
       <c r="F92">
-        <v>304.65</v>
+        <v>308.035</v>
       </c>
       <c r="G92">
         <v>9.84</v>
@@ -8825,28 +8825,28 @@
         <v>21.6</v>
       </c>
       <c r="M92">
-        <v>71.83647000000001</v>
+        <v>72.63465300000001</v>
       </c>
       <c r="N92">
-        <v>-50.23647</v>
+        <v>-51.03465300000001</v>
       </c>
       <c r="O92">
         <v>-0</v>
       </c>
       <c r="P92">
-        <v>-50.23647</v>
+        <v>-51.03465300000001</v>
       </c>
       <c r="Q92">
-        <v>-41.83647000000001</v>
+        <v>-42.63465300000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4104412166735723</v>
+        <v>0.4509569074150804</v>
       </c>
       <c r="T92">
-        <v>7.107536019307608</v>
+        <v>7.897262243675121</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3006829260958953</v>
+        <v>0.2973787181168195</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2551641216673572</v>
+        <v>0.2570641216673573</v>
       </c>
       <c r="C93">
-        <v>-230.0293129857648</v>
+        <v>-234.0273598405969</v>
       </c>
       <c r="D93">
-        <v>68.16568701423525</v>
+        <v>67.5526401594031</v>
       </c>
       <c r="E93">
-        <v>155.435</v>
+        <v>158.82</v>
       </c>
       <c r="F93">
-        <v>308.035</v>
+        <v>311.42</v>
       </c>
       <c r="G93">
         <v>9.84</v>
@@ -8907,28 +8907,28 @@
         <v>21.6</v>
       </c>
       <c r="M93">
-        <v>72.63465300000001</v>
+        <v>73.43283600000001</v>
       </c>
       <c r="N93">
-        <v>-51.03465300000001</v>
+        <v>-51.83283600000001</v>
       </c>
       <c r="O93">
         <v>-0</v>
       </c>
       <c r="P93">
-        <v>-51.03465300000001</v>
+        <v>-51.83283600000001</v>
       </c>
       <c r="Q93">
-        <v>-42.63465300000001</v>
+        <v>-43.43283600000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4509569074150804</v>
+        <v>0.5016015208419656</v>
       </c>
       <c r="T93">
-        <v>7.897262243675121</v>
+        <v>8.884420024134515</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2973787181168195</v>
+        <v>0.2941463407459846</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2570641216673573</v>
+        <v>0.2589641216673572</v>
       </c>
       <c r="C94">
-        <v>-234.0273598405969</v>
+        <v>-238.0144781300112</v>
       </c>
       <c r="D94">
-        <v>67.5526401594031</v>
+        <v>66.95052186998875</v>
       </c>
       <c r="E94">
-        <v>158.82</v>
+        <v>162.205</v>
       </c>
       <c r="F94">
-        <v>311.42</v>
+        <v>314.805</v>
       </c>
       <c r="G94">
         <v>9.84</v>
@@ -8989,28 +8989,28 @@
         <v>21.6</v>
       </c>
       <c r="M94">
-        <v>73.43283600000001</v>
+        <v>74.231019</v>
       </c>
       <c r="N94">
-        <v>-51.83283600000001</v>
+        <v>-52.631019</v>
       </c>
       <c r="O94">
         <v>-0</v>
       </c>
       <c r="P94">
-        <v>-51.83283600000001</v>
+        <v>-52.631019</v>
       </c>
       <c r="Q94">
-        <v>-43.43283600000001</v>
+        <v>-44.231019</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5016015208419656</v>
+        <v>0.5667160238193892</v>
       </c>
       <c r="T94">
-        <v>8.884420024134515</v>
+        <v>10.15362288472516</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2941463407459846</v>
+        <v>0.2909834768669954</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2589641216673572</v>
+        <v>0.2608641216673572</v>
       </c>
       <c r="C95">
-        <v>-238.0144781300112</v>
+        <v>-241.9909575016831</v>
       </c>
       <c r="D95">
-        <v>66.95052186998875</v>
+        <v>66.35904249831685</v>
       </c>
       <c r="E95">
-        <v>162.205</v>
+        <v>165.59</v>
       </c>
       <c r="F95">
-        <v>314.805</v>
+        <v>318.19</v>
       </c>
       <c r="G95">
         <v>9.84</v>
@@ -9071,28 +9071,28 @@
         <v>21.6</v>
       </c>
       <c r="M95">
-        <v>74.231019</v>
+        <v>75.029202</v>
       </c>
       <c r="N95">
-        <v>-52.631019</v>
+        <v>-53.429202</v>
       </c>
       <c r="O95">
         <v>-0</v>
       </c>
       <c r="P95">
-        <v>-52.631019</v>
+        <v>-53.429202</v>
       </c>
       <c r="Q95">
-        <v>-44.231019</v>
+        <v>-45.029202</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5667160238193892</v>
+        <v>0.653535361122621</v>
       </c>
       <c r="T95">
-        <v>10.15362288472516</v>
+        <v>11.84589336551269</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2909834768669954</v>
+        <v>0.2878879079641551</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2608641216673572</v>
+        <v>0.2627641216673572</v>
       </c>
       <c r="C96">
-        <v>-241.9909575016831</v>
+        <v>-245.9570774572679</v>
       </c>
       <c r="D96">
-        <v>66.35904249831685</v>
+        <v>65.77792254273216</v>
       </c>
       <c r="E96">
-        <v>165.59</v>
+        <v>168.9750000000001</v>
       </c>
       <c r="F96">
-        <v>318.19</v>
+        <v>321.575</v>
       </c>
       <c r="G96">
         <v>9.84</v>
@@ -9153,28 +9153,28 @@
         <v>21.6</v>
       </c>
       <c r="M96">
-        <v>75.029202</v>
+        <v>75.82738500000002</v>
       </c>
       <c r="N96">
-        <v>-53.429202</v>
+        <v>-54.22738500000002</v>
       </c>
       <c r="O96">
         <v>-0</v>
       </c>
       <c r="P96">
-        <v>-53.429202</v>
+        <v>-54.22738500000002</v>
       </c>
       <c r="Q96">
-        <v>-45.029202</v>
+        <v>-45.82738500000002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.653535361122621</v>
+        <v>0.7750824333471455</v>
       </c>
       <c r="T96">
-        <v>11.84589336551269</v>
+        <v>14.21507203861523</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2878879079641551</v>
+        <v>0.2848575089329534</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2627641216673572</v>
+        <v>0.2646641216673573</v>
       </c>
       <c r="C97">
-        <v>-245.9570774572679</v>
+        <v>-249.9131077927979</v>
       </c>
       <c r="D97">
-        <v>65.77792254273216</v>
+        <v>65.20689220720215</v>
       </c>
       <c r="E97">
-        <v>168.9750000000001</v>
+        <v>172.36</v>
       </c>
       <c r="F97">
-        <v>321.575</v>
+        <v>324.96</v>
       </c>
       <c r="G97">
         <v>9.84</v>
@@ -9235,28 +9235,28 @@
         <v>21.6</v>
       </c>
       <c r="M97">
-        <v>75.82738500000002</v>
+        <v>76.62556800000002</v>
       </c>
       <c r="N97">
-        <v>-54.22738500000002</v>
+        <v>-55.02556800000001</v>
       </c>
       <c r="O97">
         <v>-0</v>
       </c>
       <c r="P97">
-        <v>-54.22738500000002</v>
+        <v>-55.02556800000001</v>
       </c>
       <c r="Q97">
-        <v>-45.82738500000002</v>
+        <v>-46.62556800000002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7750824333471455</v>
+        <v>0.9574030416839323</v>
       </c>
       <c r="T97">
-        <v>14.21507203861523</v>
+        <v>17.76884004826905</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2848575089329534</v>
+        <v>0.2818902432149019</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2646641216673573</v>
+        <v>0.2665641216673573</v>
       </c>
       <c r="C98">
-        <v>-249.9131077927978</v>
+        <v>-253.8593090163388</v>
       </c>
       <c r="D98">
-        <v>65.20689220720215</v>
+        <v>64.64569098366111</v>
       </c>
       <c r="E98">
-        <v>172.36</v>
+        <v>175.745</v>
       </c>
       <c r="F98">
-        <v>324.96</v>
+        <v>328.345</v>
       </c>
       <c r="G98">
         <v>9.84</v>
@@ -9317,28 +9317,28 @@
         <v>21.6</v>
       </c>
       <c r="M98">
-        <v>76.625568</v>
+        <v>77.423751</v>
       </c>
       <c r="N98">
-        <v>-55.025568</v>
+        <v>-55.82375099999999</v>
       </c>
       <c r="O98">
         <v>-0</v>
       </c>
       <c r="P98">
-        <v>-55.025568</v>
+        <v>-55.82375099999999</v>
       </c>
       <c r="Q98">
-        <v>-46.625568</v>
+        <v>-47.423751</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9574030416839298</v>
+        <v>1.26127072224524</v>
       </c>
       <c r="T98">
-        <v>17.768840048269</v>
+        <v>23.69178673102534</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2818902432149019</v>
+        <v>0.2789841582333049</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2665641216673573</v>
+        <v>0.2684641216673572</v>
       </c>
       <c r="C99">
-        <v>-253.8593090163388</v>
+        <v>-257.7959327442624</v>
       </c>
       <c r="D99">
-        <v>64.64569098366111</v>
+        <v>64.09406725573764</v>
       </c>
       <c r="E99">
-        <v>175.745</v>
+        <v>179.13</v>
       </c>
       <c r="F99">
-        <v>328.345</v>
+        <v>331.73</v>
       </c>
       <c r="G99">
         <v>9.84</v>
@@ -9399,28 +9399,28 @@
         <v>21.6</v>
       </c>
       <c r="M99">
-        <v>77.423751</v>
+        <v>78.221934</v>
       </c>
       <c r="N99">
-        <v>-55.82375099999999</v>
+        <v>-56.621934</v>
       </c>
       <c r="O99">
         <v>-0</v>
       </c>
       <c r="P99">
-        <v>-55.82375099999999</v>
+        <v>-56.621934</v>
       </c>
       <c r="Q99">
-        <v>-47.423751</v>
+        <v>-48.221934</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.26127072224524</v>
+        <v>1.86900608336786</v>
       </c>
       <c r="T99">
-        <v>23.69178673102534</v>
+        <v>35.537680096538</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2789841582333049</v>
+        <v>0.2761373811084753</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2684641216673572</v>
+        <v>0.2703641216673572</v>
       </c>
       <c r="C100">
-        <v>-257.7959327442624</v>
+        <v>-261.7232220774012</v>
       </c>
       <c r="D100">
-        <v>64.09406725573764</v>
+        <v>63.5517779225988</v>
       </c>
       <c r="E100">
-        <v>179.13</v>
+        <v>182.515</v>
       </c>
       <c r="F100">
-        <v>331.73</v>
+        <v>335.115</v>
       </c>
       <c r="G100">
         <v>9.84</v>
@@ -9481,28 +9481,28 @@
         <v>21.6</v>
       </c>
       <c r="M100">
-        <v>78.221934</v>
+        <v>79.020117</v>
       </c>
       <c r="N100">
-        <v>-56.621934</v>
+        <v>-57.420117</v>
       </c>
       <c r="O100">
         <v>-0</v>
       </c>
       <c r="P100">
-        <v>-56.621934</v>
+        <v>-57.420117</v>
       </c>
       <c r="Q100">
-        <v>-48.221934</v>
+        <v>-49.020117</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.86900608336786</v>
+        <v>3.692212166735719</v>
       </c>
       <c r="T100">
-        <v>35.537680096538</v>
+        <v>71.07536019307601</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2761373811084753</v>
+        <v>0.2733481146326321</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2703641216673572</v>
-      </c>
-      <c r="C101">
-        <v>-261.7232220774012</v>
-      </c>
-      <c r="D101">
-        <v>63.5517779225988</v>
-      </c>
-      <c r="E101">
-        <v>182.515</v>
-      </c>
-      <c r="F101">
-        <v>335.115</v>
-      </c>
-      <c r="G101">
-        <v>9.84</v>
-      </c>
-      <c r="H101">
-        <v>185.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>30</v>
-      </c>
-      <c r="K101">
-        <v>8.4</v>
-      </c>
-      <c r="L101">
-        <v>21.6</v>
-      </c>
-      <c r="M101">
-        <v>79.020117</v>
-      </c>
-      <c r="N101">
-        <v>-57.420117</v>
-      </c>
-      <c r="O101">
-        <v>-0</v>
-      </c>
-      <c r="P101">
-        <v>-57.420117</v>
-      </c>
-      <c r="Q101">
-        <v>-49.020117</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.692212166735719</v>
-      </c>
-      <c r="T101">
-        <v>71.07536019307601</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0</v>
-      </c>
-      <c r="W101">
-        <v>0.2358</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2733481146326321</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
